--- a/Rules/Mage Knight Card and Skill texts .xlsx
+++ b/Rules/Mage Knight Card and Skill texts .xlsx
@@ -5,28 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\futur\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steven.Miller\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4699FB93-665C-4D97-8079-51400875C8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC8D39-88EA-4E94-97D8-6F4E26FD2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28725" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Advanced Actions" sheetId="1" r:id="rId1"/>
-    <sheet name="Skills" sheetId="3" r:id="rId2"/>
-    <sheet name="Faction Rewards" sheetId="4" r:id="rId3"/>
-    <sheet name="Enemy Attributes" sheetId="5" r:id="rId4"/>
+    <sheet name="Starting Cards" sheetId="9" r:id="rId1"/>
+    <sheet name="Advanced Actions" sheetId="1" r:id="rId2"/>
+    <sheet name="Spells" sheetId="6" r:id="rId3"/>
+    <sheet name="Artifacts" sheetId="7" r:id="rId4"/>
+    <sheet name="Units" sheetId="8" r:id="rId5"/>
+    <sheet name="Skills" sheetId="3" r:id="rId6"/>
+    <sheet name="Faction Rewards" sheetId="4" r:id="rId7"/>
+    <sheet name="Enemy Attributes" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Advanced Actions'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Advanced Actions'!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="982">
   <si>
     <t>Set</t>
   </si>
@@ -2899,12 +2903,615 @@
   <si>
     <t>After taking the first Wound to your hand this turn, throw it away and draw a card. For each of the next three Wounds you take, draw a card.</t>
   </si>
+  <si>
+    <t>Fireball / Firestorm</t>
+  </si>
+  <si>
+    <t>Ranged Fire Attack 5.</t>
+  </si>
+  <si>
+    <t>Take a Wound. Siege Fire Attack 8.</t>
+  </si>
+  <si>
+    <t>Card Name</t>
+  </si>
+  <si>
+    <t>Powered Spell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged Ice Attack 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take a Wound. Siege Ice Attack 8. </t>
+  </si>
+  <si>
+    <t>Snowstorm / Blizzard</t>
+  </si>
+  <si>
+    <t>Target enemy loses all fortifications and resistances this combat. Ranged Attack 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemies lose all fortifications this combat, or enemies lose all resistances this combat. Ranged Attack 3. </t>
+  </si>
+  <si>
+    <t>Expose / Mass Expose</t>
+  </si>
+  <si>
+    <t>Tremor / Earthquake</t>
+  </si>
+  <si>
+    <t>Flame Wall / Flame Wave</t>
+  </si>
+  <si>
+    <t>Mana Bolt / Mana Thunderbolt</t>
+  </si>
+  <si>
+    <t>Whirlwind / Tornado</t>
+  </si>
+  <si>
+    <t>Underground Travel / Underground Attack</t>
+  </si>
+  <si>
+    <t>Burning Shield / Exploding Shield</t>
+  </si>
+  <si>
+    <t>Chill / Lethal Chill</t>
+  </si>
+  <si>
+    <t>Wings of Wind / Wings of Night</t>
+  </si>
+  <si>
+    <t>Restoration / Rebirth</t>
+  </si>
+  <si>
+    <t>Demolish / Disintegrate</t>
+  </si>
+  <si>
+    <t>Space Bending / Time Bending</t>
+  </si>
+  <si>
+    <t>Call to Arms / Call to Glory</t>
+  </si>
+  <si>
+    <t>Meditation / Trance</t>
+  </si>
+  <si>
+    <t>Mana Meltdown / Mana Radiance</t>
+  </si>
+  <si>
+    <t>Mana Claim / Mana Curse</t>
+  </si>
+  <si>
+    <t>Mind Read / Mind Steal</t>
+  </si>
+  <si>
+    <t>Energy Flow / Energy Steal</t>
+  </si>
+  <si>
+    <t>Offering / Sacrifice</t>
+  </si>
+  <si>
+    <t>Mist Form / Veil of Mist</t>
+  </si>
+  <si>
+    <t>Charm / Possess</t>
+  </si>
+  <si>
+    <t>Cure / Disease</t>
+  </si>
+  <si>
+    <t>Target enemy gets Armor -3, or all enemies get Armor -2. Armor cannot be reduced below 1.</t>
+  </si>
+  <si>
+    <t>Target enemy gets Armor -3 (Armor -6 if it is fortified), or all enemies get Armor -2 (Armor -4 if they are fortified). Armor cannot be reduced below 1.</t>
+  </si>
+  <si>
+    <t>Basic Spell</t>
+  </si>
+  <si>
+    <t>Fire Attack 5 or Fire Block 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Attack 5 or Fire Block 7. This attack or block gets increased by 2 for each enemy token you are facing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you play this, pay a mana. If you paid blue, Ice Attack 8. If you paid red, Cold Fire Attack 7. If you paid white, Ranged Ice Attack 6. If you paid green, Siege Ice Attack 5. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you play this, pay a mana. If you paid blue, Ice Attack 11. If you paid red, Cold Fire Attack 10. If you paid white, Ranged Ice Attack 9. If you paid green, Siege Ice Attack 8. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy does not attack this combat. </t>
+  </si>
+  <si>
+    <t>Play this only in the Attack phase of combat. Destroy target enemy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move by up to 3 revealed spaces on the map. You may not move to or through swamps or lakes this way, and you must end your move on a safe space. Moving this way does not provoke rampaging enemies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect, except you have to end your move on a fortified site (or on a space occupied by another player). It ends your movement and counts as an assault (or as an attack on that player). Ignore site fortifications. If withdrawing after the combat, return to your original position. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Block 4. If this card is used as part of a successful Block, you may use it during your Attack phase as Fire Attack 4. </t>
+  </si>
+  <si>
+    <t>Fire Block 4. If this card is used as part of a successful Block, destroy the blocked enemy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy does not attack this combat. If it has Fire Resistance, it loses it for the rest of the turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy does not attack this combat and gets Armor -4 (to a minimum of 1) for the rest of the turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you play this, spend 1-5 Move points and move one revealed space on the map for each. You must end your move in a safe space. Moving this way does not provoke rampaging enemies. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play this during combat. If you entered combat with at least as many unspent Move points as the number of enemies you are facing, skip the Block and Assign Damage phases of this combat. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 3. If you are in a forest, Heal 5 instead. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 3. If you are in a forest, Heal 5 instead. Ready up to 3 levels worth of Units. If you are in a forest, Ready up to 5 levels of Units instead. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignore site fortifications this turn. Enemies get Armor -1 (to a minimum of 1). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play this only in the Attack phase of combat. Destroy target enemy. Other enemies get Armor -1 (to a minimum of 1). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This turn, you may move to spaces and explore new tiles that are 2 spaces away from you as if they were adjacent. Ignore any spaces you leap over this way. Your movement does not provoke rampaging enemies this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the end of your turn, set this card aside for the rest of the Round. Put all other cards you played this turn (not those discarded or thrown away) back in your hand. Skip the "draw new cards" portion of your end of turn step. Immediately take another turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You may use an ability of one Unit in the Units offer this turn, as if it were one of your recruits. You cannot assign damage to this Unit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruit any one Unit from the Units offer for free. (If you are at your Command limit, you must disband one of your Units first.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Randomly pick two cards from your discard pile and place them either on the top or bottom of your Deed deck. At the end of this turn, draw two cards over your hand limit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect, except you choose the cards instead of picking them randomly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each other player must randomly choose a crystal in their Inventory to be lost. You may gain one crystal lost this way to your Inventory. Any player that had no crystal in their Inventory when you played this, takes a Wound instead. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you play this, choose a basic mana color. Each player, including you, takes a Wound for each crystal of that color they own. Gain two crystal of the chosen color to your Inventory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take a mana die of a basic color from the Source and keep it in your Play area until the end of the Round. You can either gain 3 mana tokens of that color this turn, or one mana token of that color each turn for the remainder of the Round (starting with your next turn). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect. In addition, until the end of the Round: Each time another player uses one or more mana of that color on their turn (from any source), they take a Wound. Each player can get only one Wound per turn this way. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a color. Gain a crystal of the chosen color to your Inventory. Each other player must discard a Spell or Action card of that color from their hand, or reveal their hand to show that they have none. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect. In addition to that , you may decide to permanently steal one of the Action cards (not Spells) discarded this way and put it into your hand. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready a Unit. If you do, you may spend one Unit of level II or less in each other player's Unit area. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready a Unit. If you do, that Unit also gets Healed, and you may spend one unit of level III or less in each other player's Unit area. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a red crystal to your Inventory. You may discard up to 3 non-Wound cards from your hand. For each discarded card gain a crystal of the matching color to your Inventory (for Artifacts you choose). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose green or white, then choose red or blue. Gain Siege Attack 4 (if you choose green) or Ranged Attack 6 (if you choose white) for each pair of crystals of one of each of these colors in your Inventory. This Attack is Fire (if you choose red) or Ice (if you choose blue). Then, turn all these crystal pairs into mana. </t>
+  </si>
+  <si>
+    <t>Move 4. The Move costs of all terrains, including lakes, is 2. You cannot enter hills and mountains for the rest of this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All your Units gain all resistances. Your hero ignores the first Wound from enemies this turn. Also ignore any additional effects of that wound. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence 4. If you use this during interaction then either gain a crystal of any color to your Inventory or get a discount of 3 towards of one Unit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">One enemy does not attack. In the Attack phase gain Attack equal to its Attack including elements (if any) but ignore special abilites. You can target only other enemies with that attack. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 2. Draw a card for each Wound healed from your hand this turn, and ready each Unit healed this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All enemies blocked during the Block phase get their Armor reduced to 1. </t>
+  </si>
+  <si>
+    <t>Destroyed Effect</t>
+  </si>
+  <si>
+    <t>Banner of Glory</t>
+  </si>
+  <si>
+    <t>Banner of Fear</t>
+  </si>
+  <si>
+    <t>Banner of Protection</t>
+  </si>
+  <si>
+    <t>Banner of Courage</t>
+  </si>
+  <si>
+    <t>Ruby Ring</t>
+  </si>
+  <si>
+    <t>Sapphire Ring</t>
+  </si>
+  <si>
+    <t>Diamond Ring</t>
+  </si>
+  <si>
+    <t>Emerald Ring</t>
+  </si>
+  <si>
+    <t>Sword of Justice</t>
+  </si>
+  <si>
+    <t>Horn of Wrath</t>
+  </si>
+  <si>
+    <t>Golden Grail</t>
+  </si>
+  <si>
+    <t>Endless Bag of Gold</t>
+  </si>
+  <si>
+    <t>Endless Gem Pouch</t>
+  </si>
+  <si>
+    <t>Book of Wisdom</t>
+  </si>
+  <si>
+    <t>Amulet of Sun</t>
+  </si>
+  <si>
+    <t>Amulet of Darkness</t>
+  </si>
+  <si>
+    <t>Bow of Starsdawn</t>
+  </si>
+  <si>
+    <t>Banner of Command</t>
+  </si>
+  <si>
+    <t>Banner of Fortitude</t>
+  </si>
+  <si>
+    <t>Soul Harvester</t>
+  </si>
+  <si>
+    <t>Shield of the Fallen Kings</t>
+  </si>
+  <si>
+    <t>Druidic Staff</t>
+  </si>
+  <si>
+    <t>Circlet of Proficiency</t>
+  </si>
+  <si>
+    <t>Tome of All Spells</t>
+  </si>
+  <si>
+    <t>Mysterious Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control.
+The assigned unit gets armor +1 and +1 to any attacks or blocks it makes. Whenever this unit attacks or blocks, fame +1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units you control get armor +1 and +1 to any attacks or blocks they make this turn.
+Fame +1 for each unit that attacks or blocks this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control.
+During the block phase of combat, you may spend this unit to cancel one attack. If you do, fame +1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip the block and damage assigning phases of this combat. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control.
+The assigned unit gets armor +1, fire resistance and ice resistance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the end of your turn, you may throw away all wounds you received this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control.
+Once a round, except during combat, you may flip this card face down to ready this unit. At the beginning of a round, flip it face up again. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You may play this any time other than combat to ready all units you control. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a red mana token and a red crystal to your Inventory. Fame +1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an endless supply of red and black mana this turn. Fame +1 for each red Spell you cast this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a blue mana token and a blue crystal to your Inventory. Fame +1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an endless supply of blue and black mana this turn. Fame +1 for each blue Spell you cast this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a white mana token and a white crystal to your Inventory. Fame +1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an endless supply of white and black mana this turn. Fame +1 for each white Spell you cast this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a green mana token and a green crystal to your Inventory. Fame +1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have an endless supply of green and black mana this turn. Fame +1 for each green Spell you cast this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you play this, discard any number of cards from your hand.
+You get Attack 3 for each card you discard this way. Fame +1 for each enemy you defeat this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double the contribution of all physical attacks you play during your Attack phase this turn.
+Enemies lose physical resistance this turn. Fame +1 for each enemy you defeat this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege Attack 6.
+Roll a mana die. If you roll black or red, you get a Wound. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege Attack 6.
+You may add up to +6 to this Siege Attack. For each +1 you added roll a mana die. You get a Wound for each black or red rolled. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 2.
+Fame +1 for each point of Healing provided by this card you spend this turn. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 6.
+Every time you Heal a Wound from hand this turn, draw a card. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence 4, Fame +2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence 9, Fame +3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roll a mana die two times.
+Gain a crystal to your Inventory for each color rolled this way (if you roll gold, you choose the color). If you roll black, Fame +1 instead of a crystal. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a mana token of each basic color.
+Also get one gold (if played at day) or black (if played at night) mana token. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throw away an Action card from your hand. Gain an Advanced Action card from the Advanced Actions offer to your hand that is the same color as the Action you threw away. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throw away an Action card from your hand. Gain a Spell from the Spells offer to your hand that is the same color as the Action you threw away and a Crystal of that color to your Inventory. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a gold mana token.
+If played during the Night, forests have their move cost reduced to 3, you can use gold mana, and you reveal garrisons of nearby fortified sites and all ruins as if it were day. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect, except you get three gold mana tokens instead of one. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a mana token of any color.
+If played during the Day, deserts have their move cost reduced to 3 and you can use black mana as if it were Night. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the basic effect, except you get three mana tokens of any colors instead of one. </t>
+  </si>
+  <si>
+    <t>When you play this, discard any amount of cards from your hand.  You get Ranged Attack 2 for each card you discard this way.  Fame 1 for each enemy you defeat in the current phase of combat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each of your Ranged Attacks this turn is either doubled, or becomes a Siege Attack of the same element.  You may also double any Siege attacks, but they become Ranged Attacks of the same element. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence 4.  If you recruited a Unit this turn, you may assign this card to it instead of a Command token.  Put this card face down over the Unit when it is spent, and return it face up under it whenever it is ready. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain Fame +2.  Recruit any one Unit from the Units offer for free.  (If you are at your Command limit, you must disband one of your units first.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control.
+Once a Round, when the Unit is about to get wounded, flip this card to ignore the Wound and any additional effects from it.  The Unit can still only be assigned damage once each combat. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anytime except during combat:
+Heal all of your Units completely. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack 3.  For one enemy defeated by this attack gain one crystal to your inventory. It may be red if the enemy had Fire Resistance, blue if it had Ice Resistance, green if it had Physical Resistance.  You may always choose white. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack 8.  Gain one crystal as above for each enemy defeated in the current phase of combat. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block 6, or two Block 4 against different attacks. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Fire Block 8, or up to three Cold Fire Block 4 against different attacks. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard a card.  Depending on its color, you get:
+White: Move up to 2 revealed spaces, to a safe space;
+Blue: Get two crystals of any one color;
+Red: Ready a level III Unit or lower;
+Green: Heal 3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose two of the options above, without discarding any cards. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use any non-interactive Skill in the Common Skills offer (including your own) as if it were your Skill.  If it is a Skill usable each turn (one that does not flip), use its effect twice. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take any Skill in the Common Skills offer (including your own) and keep it for the rest of the game, as if acquired through a Level Up. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard a card of any color.  Use the basic effect of a Spell of the same color from the Spells offer without paying its mana cost. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard a card of any color.  Use the stronger effect of a Spell of the same color from the Spells offer without paying its mana cost.  You may do so even during the Day. </t>
+  </si>
+  <si>
+    <t>Remove and reveal the top card of the Artifacts deck. This turn, you may use Mysterious Box as if it was that Artifact. If you do then Fame +1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the end of the turn: put the revealed Artifact on the bottom of the Artifacts deck; if you did not use Mysterious Box then put it back in your hand; if you placed it on an unit as a banner then discard it. </t>
+  </si>
+  <si>
+    <t>Silver Units</t>
+  </si>
+  <si>
+    <t>Gold Units</t>
+  </si>
+  <si>
+    <t>Fire Golems</t>
+  </si>
+  <si>
+    <t>Ice Golems</t>
+  </si>
+  <si>
+    <t>Fire Mages</t>
+  </si>
+  <si>
+    <t>Ice Mages</t>
+  </si>
+  <si>
+    <t>Amotep Gunners</t>
+  </si>
+  <si>
+    <t>Amotep Freezers</t>
+  </si>
+  <si>
+    <t>Altem Mages</t>
+  </si>
+  <si>
+    <t>Altem Guardians</t>
+  </si>
+  <si>
+    <t>Attack or Block 2</t>
+  </si>
+  <si>
+    <t>Option 1 Effect</t>
+  </si>
+  <si>
+    <t>Option 2 Effect</t>
+  </si>
+  <si>
+    <t>Option 3 Effect</t>
+  </si>
+  <si>
+    <t>Influence 2</t>
+  </si>
+  <si>
+    <t>Move 2</t>
+  </si>
+  <si>
+    <t>Option 1 Extra Cost</t>
+  </si>
+  <si>
+    <t>Option 2 Extra Cost</t>
+  </si>
+  <si>
+    <t>Option 3 Extra Cost</t>
+  </si>
+  <si>
+    <t>Ready a level I or II Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a green mana token </t>
+  </si>
+  <si>
+    <t>Delphana Masters</t>
+  </si>
+  <si>
+    <t>Sorcerers</t>
+  </si>
+  <si>
+    <t>Heroes (red)</t>
+  </si>
+  <si>
+    <t>Heroes (blue)</t>
+  </si>
+  <si>
+    <t>Heroes (green)</t>
+  </si>
+  <si>
+    <t>Heroes (white)</t>
+  </si>
+  <si>
+    <t>Catapults</t>
+  </si>
+  <si>
+    <t>Magic Familiars</t>
+  </si>
+  <si>
+    <t>Shocktroops</t>
+  </si>
+  <si>
+    <t>Thugs</t>
+  </si>
+  <si>
+    <t>Scouts</t>
+  </si>
+  <si>
+    <t>Savage Monks</t>
+  </si>
+  <si>
+    <t>Northern Monks</t>
+  </si>
+  <si>
+    <t>Red Cape Monks</t>
+  </si>
+  <si>
+    <t>Illusionists</t>
+  </si>
+  <si>
+    <t>Guardian Golems</t>
+  </si>
+  <si>
+    <t>Utem Swordsmen</t>
+  </si>
+  <si>
+    <t>Utem Guardsmen</t>
+  </si>
+  <si>
+    <t>Utem Crossbowmen</t>
+  </si>
+  <si>
+    <t>Foresters</t>
+  </si>
+  <si>
+    <t>Herbalists</t>
+  </si>
+  <si>
+    <t>Peasants</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2944,6 +3551,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2975,7 +3589,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3048,12 +3662,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3064,29 +3687,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3095,9 +3751,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3109,47 +3762,51 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3453,916 +4110,943 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38EE428A-3648-43AA-871D-84443E02FB62}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="112.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="105.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="14.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="112.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="105.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="12" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="14" t="s">
         <v>724</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="12" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="14" t="s">
         <v>762</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="12" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="14" t="s">
         <v>695</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="12" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="14" t="s">
         <v>707</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="12" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="14" t="s">
         <v>710</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="12" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="12" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="12" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="14" t="s">
         <v>704</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="12" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="31" t="s">
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="14" t="s">
         <v>701</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="12" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="14" t="s">
         <v>698</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="12" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="14" t="s">
         <v>720</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="12" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
+    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="14" t="s">
         <v>714</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="12" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="31" t="s">
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="12" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="12" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="31" t="s">
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="14" t="s">
         <v>771</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="12" t="s">
         <v>772</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="12" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="20" t="s">
         <v>734</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="12" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="31" t="s">
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="14" t="s">
         <v>731</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="12" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="31" t="s">
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="12" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="31" t="s">
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="14" t="s">
         <v>728</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="12" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="31" t="s">
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="14" t="s">
         <v>774</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="12" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="14" t="s">
         <v>777</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="12" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="31" t="s">
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="14" t="s">
         <v>735</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="12" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="31" t="s">
+    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="14" t="s">
         <v>744</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="12" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="31" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="14" t="s">
         <v>768</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="12" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="31" t="s">
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="14" t="s">
         <v>741</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="14" t="s">
         <v>742</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="12" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="31" t="s">
+    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="14" t="s">
         <v>755</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="14" t="s">
         <v>756</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="12" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="31" t="s">
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="20" t="s">
         <v>784</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="14" t="s">
         <v>780</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="12" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="14" t="s">
         <v>783</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="12" t="s">
         <v>787</v>
       </c>
     </row>
@@ -4376,19 +5060,956 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4487065-31BB-45F2-B223-F2A0D1499038}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="61.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.85546875" style="37"/>
+    <col min="5" max="5" width="52.28515625" style="37" customWidth="1"/>
+    <col min="6" max="16384" width="61.85546875" style="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>822</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>788</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>789</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="33"/>
+      <c r="B3" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>795</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>793</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="33" t="s">
+        <v>798</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>796</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="33" t="s">
+        <v>799</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>820</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="33"/>
+      <c r="B6" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>800</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="33"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="33" t="s">
+        <v>801</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>825</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="33"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="33" t="s">
+        <v>802</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>827</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="33" t="s">
+        <v>803</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>829</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
+      <c r="B10" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>804</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>831</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>805</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
+      <c r="B12" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>806</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>835</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="33"/>
+      <c r="B13" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>807</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>837</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
+      <c r="B14" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>808</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>839</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="33"/>
+      <c r="B15" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>809</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="33" t="s">
+        <v>810</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>843</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="33"/>
+      <c r="B17" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>845</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="33"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="33" t="s">
+        <v>812</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>847</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="33"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="33" t="s">
+        <v>813</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>849</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="33" t="s">
+        <v>814</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>851</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="33" t="s">
+        <v>815</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>853</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="33"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="33" t="s">
+        <v>816</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>855</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="33"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="33" t="s">
+        <v>817</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>857</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="33"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="33" t="s">
+        <v>818</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>859</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="33"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="33" t="s">
+        <v>819</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>861</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>862</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1518E3E-453A-4819-AA88-E10B951A9C6F}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="40.85546875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="42" t="s">
+        <v>864</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="42" t="s">
+        <v>865</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="42" t="s">
+        <v>868</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="42" t="s">
+        <v>870</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="42" t="s">
+        <v>871</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="42" t="s">
+        <v>872</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="42" t="s">
+        <v>873</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="42" t="s">
+        <v>874</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="42" t="s">
+        <v>875</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="42" t="s">
+        <v>876</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>913</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="42" t="s">
+        <v>877</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="42" t="s">
+        <v>878</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="42" t="s">
+        <v>879</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="42" t="s">
+        <v>880</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="42" t="s">
+        <v>881</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="42" t="s">
+        <v>882</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>925</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="42" t="s">
+        <v>883</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>927</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="42" t="s">
+        <v>884</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="42" t="s">
+        <v>885</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="42" t="s">
+        <v>886</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="42" t="s">
+        <v>887</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="42" t="s">
+        <v>888</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>937</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>938</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523F47E6-7E6F-4E51-BCA8-02BFAECA2517}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>950</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>956</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>951</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>957</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>939</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="32" t="s">
+        <v>981</v>
+      </c>
+      <c r="D3" t="s">
+        <v>949</v>
+      </c>
+      <c r="F3" t="s">
+        <v>953</v>
+      </c>
+      <c r="H3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="32" t="s">
+        <v>980</v>
+      </c>
+      <c r="D4" t="s">
+        <v>958</v>
+      </c>
+      <c r="F4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="32" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="32" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="32" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="32" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="32" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="32" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="32" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="32" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="32" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="32" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="32" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="32" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="43" t="s">
+        <v>940</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="32" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="32" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="32" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="32" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="32" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="32" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="32" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="32" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="32" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="32" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="32" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="32" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="32" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="32" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="32" t="s">
+        <v>960</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A18:H18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6CAB4A-A364-4A18-B7EC-71D43CA49563}">
   <dimension ref="A1:D172"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="101.6640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="97.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="8.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="97.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>404</v>
       </c>
@@ -4402,2039 +6023,2034 @@
         <v>401</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+    </row>
+    <row r="3" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>410</v>
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>411</v>
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>412</v>
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>413</v>
       </c>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>414</v>
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>415</v>
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>416</v>
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>421</v>
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-    </row>
-    <row r="15" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+    </row>
+    <row r="15" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>422</v>
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46187</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>423</v>
       </c>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>424</v>
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>425</v>
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>426</v>
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>427</v>
       </c>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>428</v>
       </c>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>429</v>
       </c>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9">
+    <row r="25" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <v>676856</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>434</v>
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-    </row>
-    <row r="27" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+    </row>
+    <row r="27" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>435</v>
       </c>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>866002</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>436</v>
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>437</v>
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>438</v>
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>439</v>
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>440</v>
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>441</v>
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>442</v>
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>171244</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>447</v>
       </c>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="14"/>
-    </row>
-    <row r="39" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+    </row>
+    <row r="39" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>448</v>
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>449</v>
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>450</v>
       </c>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>451</v>
       </c>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>452</v>
       </c>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>453</v>
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>454</v>
       </c>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>455</v>
       </c>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="7" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>460</v>
       </c>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="12" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="14"/>
-    </row>
-    <row r="51" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
+    </row>
+    <row r="51" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>210835</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>461</v>
       </c>
       <c r="D51" s="6"/>
     </row>
-    <row r="52" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="7" t="s">
         <v>462</v>
       </c>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>463</v>
       </c>
       <c r="D53" s="6"/>
     </row>
-    <row r="54" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>464</v>
       </c>
       <c r="D54" s="6"/>
     </row>
-    <row r="55" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>465</v>
       </c>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="7" t="s">
         <v>466</v>
       </c>
       <c r="D56" s="6"/>
     </row>
-    <row r="57" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>467</v>
       </c>
       <c r="D57" s="6"/>
     </row>
-    <row r="58" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>468</v>
       </c>
       <c r="D58" s="6"/>
     </row>
-    <row r="59" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>564392</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>473</v>
       </c>
       <c r="D61" s="6"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="12" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="14"/>
-    </row>
-    <row r="63" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="25"/>
+    </row>
+    <row r="63" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>474</v>
       </c>
       <c r="D63" s="6"/>
     </row>
-    <row r="64" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>475</v>
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="7" t="s">
         <v>476</v>
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="7" t="s">
         <v>477</v>
       </c>
       <c r="D66" s="6"/>
     </row>
-    <row r="67" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>478</v>
       </c>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>893537</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="7" t="s">
         <v>479</v>
       </c>
       <c r="D68" s="6"/>
     </row>
-    <row r="69" spans="1:4" ht="179.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>480</v>
       </c>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>481</v>
       </c>
       <c r="D70" s="6"/>
     </row>
-    <row r="71" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="7" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="7" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="138" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>958209</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="7" t="s">
         <v>486</v>
       </c>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="12" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
-    </row>
-    <row r="75" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="25"/>
+    </row>
+    <row r="75" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>122015</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>487</v>
       </c>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="7" t="s">
         <v>488</v>
       </c>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>489</v>
       </c>
       <c r="D77" s="6"/>
     </row>
-    <row r="78" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="7" t="s">
         <v>490</v>
       </c>
       <c r="D78" s="6"/>
     </row>
-    <row r="79" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="7" t="s">
         <v>491</v>
       </c>
       <c r="D79" s="6"/>
     </row>
-    <row r="80" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>492</v>
       </c>
       <c r="D80" s="6"/>
     </row>
-    <row r="81" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>493</v>
       </c>
       <c r="D81" s="6"/>
     </row>
-    <row r="82" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>494</v>
       </c>
       <c r="D82" s="6"/>
     </row>
-    <row r="83" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="7" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="7" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="7" t="s">
         <v>498</v>
       </c>
       <c r="D85" s="6"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="23" t="s">
         <v>379</v>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="14"/>
-    </row>
-    <row r="87" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="25"/>
+    </row>
+    <row r="87" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="7" t="s">
         <v>499</v>
       </c>
       <c r="D87" s="6"/>
     </row>
-    <row r="88" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="7" t="s">
         <v>500</v>
       </c>
       <c r="D88" s="6"/>
     </row>
-    <row r="89" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="7" t="s">
         <v>501</v>
       </c>
       <c r="D89" s="6"/>
     </row>
-    <row r="90" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>502</v>
       </c>
       <c r="D90" s="6"/>
     </row>
-    <row r="91" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>6.9399999999999996E+29</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="7" t="s">
         <v>503</v>
       </c>
       <c r="D91" s="6"/>
     </row>
-    <row r="92" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="7" t="s">
         <v>504</v>
       </c>
       <c r="D92" s="6"/>
     </row>
-    <row r="93" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>505</v>
       </c>
       <c r="D93" s="6"/>
     </row>
-    <row r="94" spans="1:4" ht="165.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="153" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>506</v>
       </c>
       <c r="D94" s="6"/>
     </row>
-    <row r="95" spans="1:4" ht="207" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="7" t="s">
         <v>507</v>
       </c>
       <c r="D95" s="6"/>
     </row>
-    <row r="96" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="7" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="7" t="s">
         <v>510</v>
       </c>
       <c r="D97" s="6"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="16" t="s">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="18"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="12" t="s">
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="28"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="14"/>
-    </row>
-    <row r="100" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+      <c r="B99" s="24"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="25"/>
+    </row>
+    <row r="100" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="7" t="s">
         <v>511</v>
       </c>
       <c r="D100" s="6"/>
     </row>
-    <row r="101" spans="1:4" ht="165.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="153" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="7" t="s">
         <v>512</v>
       </c>
       <c r="D101" s="6"/>
     </row>
-    <row r="102" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="7" t="s">
         <v>513</v>
       </c>
       <c r="D102" s="6"/>
     </row>
-    <row r="103" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="7" t="s">
         <v>514</v>
       </c>
       <c r="D103" s="6"/>
     </row>
-    <row r="104" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>38787</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="7" t="s">
         <v>515</v>
       </c>
       <c r="D104" s="6"/>
     </row>
-    <row r="105" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>929377</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="7" t="s">
         <v>516</v>
       </c>
       <c r="D105" s="6"/>
     </row>
-    <row r="106" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="7" t="s">
         <v>517</v>
       </c>
       <c r="D106" s="6"/>
     </row>
-    <row r="107" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="7" t="s">
         <v>518</v>
       </c>
       <c r="D107" s="6"/>
     </row>
-    <row r="108" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="7" t="s">
         <v>519</v>
       </c>
       <c r="D108" s="6"/>
     </row>
-    <row r="109" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="7" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>335290</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="B110" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="7" t="s">
         <v>522</v>
       </c>
       <c r="D110" s="6"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="12" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="14"/>
-    </row>
-    <row r="112" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="25"/>
+    </row>
+    <row r="112" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="7" t="s">
         <v>523</v>
       </c>
       <c r="D112" s="6"/>
     </row>
-    <row r="113" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="7" t="s">
         <v>524</v>
       </c>
       <c r="D113" s="6"/>
     </row>
-    <row r="114" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="B114" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="7" t="s">
         <v>525</v>
       </c>
       <c r="D114" s="6"/>
     </row>
-    <row r="115" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="B115" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="7" t="s">
         <v>526</v>
       </c>
       <c r="D115" s="6"/>
     </row>
-    <row r="116" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="7" t="s">
         <v>527</v>
       </c>
       <c r="D116" s="6"/>
     </row>
-    <row r="117" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="7" t="s">
         <v>528</v>
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="7" t="s">
         <v>529</v>
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="7" t="s">
         <v>530</v>
       </c>
       <c r="D119" s="6"/>
     </row>
-    <row r="120" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="7" t="s">
         <v>531</v>
       </c>
       <c r="D120" s="6"/>
     </row>
-    <row r="121" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B121" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="7" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="7" t="s">
         <v>534</v>
       </c>
       <c r="D122" s="6"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="12" t="s">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="B123" s="13"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="14"/>
-    </row>
-    <row r="124" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+      <c r="B123" s="24"/>
+      <c r="C123" s="24"/>
+      <c r="D123" s="25"/>
+    </row>
+    <row r="124" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="7" t="s">
         <v>535</v>
       </c>
       <c r="D124" s="6"/>
     </row>
-    <row r="125" spans="1:4" ht="138" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="7" t="s">
         <v>536</v>
       </c>
       <c r="D125" s="6"/>
     </row>
-    <row r="126" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="7" t="s">
         <v>537</v>
       </c>
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="7" t="s">
         <v>538</v>
       </c>
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="7" t="s">
         <v>539</v>
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="7" t="s">
         <v>300</v>
       </c>
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="7" t="s">
         <v>540</v>
       </c>
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="7" t="s">
         <v>541</v>
       </c>
       <c r="D132" s="6"/>
     </row>
-    <row r="133" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>107400</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="7" t="s">
         <v>542</v>
       </c>
       <c r="D133" s="6"/>
     </row>
-    <row r="134" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="7" t="s">
         <v>543</v>
       </c>
       <c r="D134" s="6"/>
     </row>
-    <row r="135" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>676855</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="7" t="s">
         <v>544</v>
       </c>
       <c r="D135" s="6"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="12" t="s">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="14"/>
-    </row>
-    <row r="137" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+      <c r="B136" s="24"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="25"/>
+    </row>
+    <row r="137" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="B137" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="7" t="s">
         <v>545</v>
       </c>
       <c r="D137" s="6"/>
     </row>
-    <row r="138" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="7" t="s">
         <v>546</v>
       </c>
       <c r="D138" s="6"/>
     </row>
-    <row r="139" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="B139" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="7" t="s">
         <v>547</v>
       </c>
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="B140" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="7" t="s">
         <v>548</v>
       </c>
       <c r="D140" s="6"/>
     </row>
-    <row r="141" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B141" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="7" t="s">
         <v>549</v>
       </c>
       <c r="D141" s="6"/>
     </row>
-    <row r="142" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="7" t="s">
         <v>550</v>
       </c>
       <c r="D142" s="6"/>
     </row>
-    <row r="143" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="7" t="s">
         <v>551</v>
       </c>
       <c r="D143" s="6"/>
     </row>
-    <row r="144" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>933090</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="7" t="s">
         <v>552</v>
       </c>
       <c r="D144" s="6"/>
     </row>
-    <row r="145" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B145" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="7" t="s">
         <v>553</v>
       </c>
       <c r="D145" s="6"/>
     </row>
-    <row r="146" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="7" t="s">
         <v>554</v>
       </c>
       <c r="D146" s="6"/>
     </row>
-    <row r="147" spans="1:4" ht="207" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B147" s="8" t="s">
+      <c r="B147" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="7" t="s">
         <v>555</v>
       </c>
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="1:4" ht="138" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="7" t="s">
         <v>556</v>
       </c>
       <c r="D148" s="6"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="12" t="s">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="B149" s="13"/>
-      <c r="C149" s="13"/>
-      <c r="D149" s="14"/>
-    </row>
-    <row r="150" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="25"/>
+    </row>
+    <row r="150" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="7" t="s">
         <v>557</v>
       </c>
       <c r="D150" s="6"/>
     </row>
-    <row r="151" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="7" t="s">
         <v>558</v>
       </c>
       <c r="D151" s="6"/>
     </row>
-    <row r="152" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="7" t="s">
         <v>559</v>
       </c>
       <c r="D152" s="6"/>
     </row>
-    <row r="153" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="7" t="s">
         <v>560</v>
       </c>
       <c r="D153" s="6"/>
     </row>
-    <row r="154" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="7" t="s">
         <v>561</v>
       </c>
       <c r="D154" s="6"/>
     </row>
-    <row r="155" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="7" t="s">
         <v>562</v>
       </c>
       <c r="D155" s="6"/>
     </row>
-    <row r="156" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>62555</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="7" t="s">
         <v>563</v>
       </c>
       <c r="D156" s="6"/>
     </row>
-    <row r="157" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="7" t="s">
         <v>564</v>
       </c>
       <c r="D157" s="6"/>
     </row>
-    <row r="158" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="7" t="s">
         <v>565</v>
       </c>
       <c r="D158" s="6"/>
     </row>
-    <row r="159" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D159" s="7" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A160" s="19" t="s">
+    <row r="160" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="7" t="s">
         <v>568</v>
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="12" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="13"/>
-      <c r="C161" s="13"/>
-      <c r="D161" s="14"/>
-    </row>
-    <row r="162" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B161" s="24"/>
+      <c r="C161" s="24"/>
+      <c r="D161" s="25"/>
+    </row>
+    <row r="162" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="7" t="s">
         <v>569</v>
       </c>
       <c r="D162" s="6"/>
     </row>
-    <row r="163" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="7" t="s">
         <v>570</v>
       </c>
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="7" t="s">
         <v>571</v>
       </c>
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="7" t="s">
         <v>572</v>
       </c>
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="B166" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="7" t="s">
         <v>573</v>
       </c>
       <c r="D166" s="6"/>
     </row>
-    <row r="167" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B167" s="8" t="s">
+      <c r="B167" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="7" t="s">
         <v>574</v>
       </c>
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="B168" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="7" t="s">
         <v>575</v>
       </c>
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="7" t="s">
         <v>576</v>
       </c>
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="B170" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="7" t="s">
         <v>577</v>
       </c>
       <c r="D170" s="6"/>
     </row>
-    <row r="171" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="102" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="D171" s="8" t="s">
+      <c r="D171" s="7" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="7" t="s">
         <v>580</v>
       </c>
       <c r="D172" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A86:D86"/>
     <mergeCell ref="A98:D98"/>
@@ -6445,323 +8061,328 @@
     <mergeCell ref="A111:D111"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A50:D50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BFD584-66AF-44F3-9DD5-44943E29E62D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="103.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="103.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="164.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="103.88671875" style="1"/>
+    <col min="1" max="1" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="164.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="103.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>593</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-    </row>
-    <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>618</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>616</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="15" t="s">
         <v>585</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="15" t="s">
         <v>588</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>617</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>621</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="15" t="s">
         <v>586</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-    </row>
-    <row r="10" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+    </row>
+    <row r="10" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="15" t="s">
         <v>583</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="15" t="s">
         <v>587</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="15" t="s">
         <v>590</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>613</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>614</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="15" t="s">
         <v>592</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
         <v>595</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-    </row>
-    <row r="17" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+    </row>
+    <row r="17" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>627</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+    <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+    <row r="20" spans="1:3" ht="51" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>623</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="15" t="s">
         <v>601</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>625</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30" t="s">
         <v>596</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-    </row>
-    <row r="24" spans="1:3" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>628</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
+    <row r="25" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>633</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+    <row r="26" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+    <row r="27" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>632</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+    <row r="28" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="15" t="s">
         <v>607</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
+    <row r="29" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>629</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="15" t="s">
         <v>608</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>657</v>
       </c>
     </row>
@@ -6776,169 +8397,169 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA0F03E-4077-4D5A-9A57-C44D6F7CF78F}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>659</v>
       </c>
-      <c r="B1" s="32"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="31"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="12" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="12" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="12" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="12" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="12" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="12" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
         <v>658</v>
       </c>
-      <c r="B9" s="27"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="B9" s="30"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="12" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="12" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>678</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="12" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>680</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="12" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="12" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="12" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="12" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="12" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>689</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="12" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="12" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="12" t="s">
         <v>694</v>
       </c>
     </row>

--- a/Rules/Mage Knight Card and Skill texts .xlsx
+++ b/Rules/Mage Knight Card and Skill texts .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steven.Miller\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18c549927b9fc512/Board Games/Mage Knight/TTS/Lua Code/Mage_Knight_Highly_Scripted/Rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC8D39-88EA-4E94-97D8-6F4E26FD2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{34FC8D39-88EA-4E94-97D8-6F4E26FD2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{244E99E0-54D9-4CC1-9F7F-322150D79929}"/>
   <bookViews>
-    <workbookView xWindow="28725" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Starting Cards" sheetId="9" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="1119">
   <si>
     <t>Set</t>
   </si>
@@ -3048,9 +3048,6 @@
     <t xml:space="preserve">When you play this, spend 1-5 Move points and move one revealed space on the map for each. You must end your move in a safe space. Moving this way does not provoke rampaging enemies. </t>
   </si>
   <si>
-    <t xml:space="preserve">Play this during combat. If you entered combat with at least as many unspent Move points as the number of enemies you are facing, skip the Block and Assign Damage phases of this combat. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Heal 3. If you are in a forest, Heal 5 instead. </t>
   </si>
   <si>
@@ -3505,6 +3502,476 @@
   </si>
   <si>
     <t>Peasants</t>
+  </si>
+  <si>
+    <t>Attack or Block 3</t>
+  </si>
+  <si>
+    <t>Ranged Attack 2</t>
+  </si>
+  <si>
+    <t>Block 3</t>
+  </si>
+  <si>
+    <t>Move 2.
+The move cost of forest, hills and swamps is reduced by 1 this turn, to a minimum of 0</t>
+  </si>
+  <si>
+    <t>Attack 2</t>
+  </si>
+  <si>
+    <t>Block 4.
+Counts twice against an attack with swiftness.</t>
+  </si>
+  <si>
+    <t>Fire Block 4</t>
+  </si>
+  <si>
+    <t>Ice Block 4</t>
+  </si>
+  <si>
+    <t>Heal 2</t>
+  </si>
+  <si>
+    <t>Green
+Mana</t>
+  </si>
+  <si>
+    <t>Red
+Mana</t>
+  </si>
+  <si>
+    <t>Blue
+Mana</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Armour</t>
+  </si>
+  <si>
+    <t>Recruit</t>
+  </si>
+  <si>
+    <t>Village
+Monestary</t>
+  </si>
+  <si>
+    <t>Mage Tower
+Keep</t>
+  </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Keep
+Village</t>
+  </si>
+  <si>
+    <t>Village</t>
+  </si>
+  <si>
+    <t>Mage Tower
+Monestary</t>
+  </si>
+  <si>
+    <t>Influence 4</t>
+  </si>
+  <si>
+    <t>White
+Mana</t>
+  </si>
+  <si>
+    <t>Target unfortified enemy does not attack this combat.</t>
+  </si>
+  <si>
+    <t>Gain a white crystal to your Inventory.</t>
+  </si>
+  <si>
+    <t>004558
+506ea7</t>
+  </si>
+  <si>
+    <t>d55e5c
+e8acd7</t>
+  </si>
+  <si>
+    <t>c1f77c
+00ebf3</t>
+  </si>
+  <si>
+    <t>db04a7
+b33811</t>
+  </si>
+  <si>
+    <t>84e5d3
+b5500d</t>
+  </si>
+  <si>
+    <t>c72d43
+8dc143</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Attack or Block 6.
+This unit becomes wounded.</t>
+  </si>
+  <si>
+    <t>c10664
+aff9b6</t>
+  </si>
+  <si>
+    <t>f17813</t>
+  </si>
+  <si>
+    <t>Monestary</t>
+  </si>
+  <si>
+    <t>Ice Attack or
+Ice Block 4</t>
+  </si>
+  <si>
+    <t>Fire Attack or
+Fire Block 4</t>
+  </si>
+  <si>
+    <t>868e12</t>
+  </si>
+  <si>
+    <t>b8d41f</t>
+  </si>
+  <si>
+    <t>Siege Attack 4</t>
+  </si>
+  <si>
+    <t>a0a6cb
+794e16
+484fa3</t>
+  </si>
+  <si>
+    <t>75307e
+422b8b</t>
+  </si>
+  <si>
+    <t>Ranged Attack 1. All your other Units get +1 to all their Attacks this turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduce Armor and one attack of chosen enemy by 1. </t>
+  </si>
+  <si>
+    <t>Reduce one enemy attack by 3. Any damage from that attack must be assigned to this Unit first, even if that enemy had Assassination.</t>
+  </si>
+  <si>
+    <t>4339c4
+ff2a54</t>
+  </si>
+  <si>
+    <t>Village
+Keep</t>
+  </si>
+  <si>
+    <t>Attack 3, Reputation -1</t>
+  </si>
+  <si>
+    <t>Influence 4, Reputation -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege Attack 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take a look at a face down token within 3 spaces on the map, or at the top token of any unused enemy token pile. If you defeat that token this turn, gain +1 Fame. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move 2. You may reveal a new tile at a distance of 2 spaces instead of 1. </t>
+  </si>
+  <si>
+    <t>Mage Tower
+Monestary
+Village
+Keep
+City</t>
+  </si>
+  <si>
+    <t>Mage Tower
+Monestary
+Glade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack 3 (+2 if the mana on the card is red) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block 4 (+3 if the mana on the card is blue) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move 3 or Influence 3 (+2 if the mana on the card is white) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heal 2 (+1 if the mana on the card is green) </t>
+  </si>
+  <si>
+    <t>Option 4 Extra Cost</t>
+  </si>
+  <si>
+    <t>Option 4 Effect</t>
+  </si>
+  <si>
+    <t>bd1011
+246b0d</t>
+  </si>
+  <si>
+    <t>0a2e0b
+d8e49b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you recruit Magic Familiars, you must also pay a mana of a basic color. Take a crystal of that color from the supply and place it on the Magic Familiars. At the start of every round, remove that crystal and replace it with a crystal of the same or a different color from your inventory. If you cannot or choose not to replace the crystal, the Magic Familiars are removed from the game. </t>
+  </si>
+  <si>
+    <t>Special Overall Card Rule</t>
+  </si>
+  <si>
+    <t>f8ebe0
+9e8205</t>
+  </si>
+  <si>
+    <t>Keep
+City</t>
+  </si>
+  <si>
+    <t>Attack or Block 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy does not attack this combat and it gets Armor -3 (to a minimum of 1). </t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>9ea578
+f80455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged Fire Attack 3 </t>
+  </si>
+  <si>
+    <t>Fire Attack or Fire Block 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a red mana token and a red crystal to your Inventory. </t>
+  </si>
+  <si>
+    <t>Ice
+Physical</t>
+  </si>
+  <si>
+    <t>c6ca7b
+18446c</t>
+  </si>
+  <si>
+    <t>Ice Attack 6</t>
+  </si>
+  <si>
+    <t>97f64a
+d81a4f</t>
+  </si>
+  <si>
+    <t>Fire
+Physical</t>
+  </si>
+  <si>
+    <t>Ranged Fire Attack 4</t>
+  </si>
+  <si>
+    <t>094bd9
+2806cf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Attack or Ice Block 4 </t>
+  </si>
+  <si>
+    <t>Siege Ice Attack 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain a blue mana token and a blue crystal to your Inventory. </t>
+  </si>
+  <si>
+    <t>f60766
+7ba7be</t>
+  </si>
+  <si>
+    <t>Ranged Fire Attack 6</t>
+  </si>
+  <si>
+    <t>bb1660
+0fe22e</t>
+  </si>
+  <si>
+    <t>Fire
+Ice</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 2 mana tokens of any colors </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Fire attack or Cold Fire Block 5. You can pay a blue or red mana to increase this to 7, or pay both to increase this to 9. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay a black mana: Choose one: All attacks you play this combat become Cold Fire Attacks, or all your attacks become Siege Attacks in addition to any elements they have. </t>
+  </si>
+  <si>
+    <t>Black
+Mana</t>
+  </si>
+  <si>
+    <t>f288e1
+5726ab
+f288ea</t>
+  </si>
+  <si>
+    <t>Attack 5</t>
+  </si>
+  <si>
+    <t>Block 8.
+Counts twice against an attack with swiftness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All units you control gain all resistances this turn. </t>
+  </si>
+  <si>
+    <t>1aa681
+d6d932
+1aa68c</t>
+  </si>
+  <si>
+    <t>Siege Attack 3</t>
+  </si>
+  <si>
+    <t>Siege Fire Attack 5</t>
+  </si>
+  <si>
+    <t>Siege Ice Attack 5</t>
+  </si>
+  <si>
+    <t>Village
+Keep
+City</t>
+  </si>
+  <si>
+    <t>Cold Fire Block 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence 5. If used during interaction, Reputation +1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have to pay 2 influence to activate this Unit during any assault or an attack on another player. </t>
+  </si>
+  <si>
+    <t>88f3f2</t>
+  </si>
+  <si>
+    <t>613dca</t>
+  </si>
+  <si>
+    <t>Heal 4</t>
+  </si>
+  <si>
+    <t>8ccbdd</t>
+  </si>
+  <si>
+    <t>Ranged Attack 7</t>
+  </si>
+  <si>
+    <t>4ee245</t>
+  </si>
+  <si>
+    <t>Cold Fire Attack 6</t>
+  </si>
+  <si>
+    <t>c3e3c5
+223b47</t>
+  </si>
+  <si>
+    <t>Ranged Attack 3</t>
+  </si>
+  <si>
+    <t>Chosen enemy loses all fortifications. Ranged Attack 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen enemy loses all resistances. Ranged Attack 3. </t>
+  </si>
+  <si>
+    <t>5c2da0
+9c5c38</t>
+  </si>
+  <si>
+    <t>Fire
+Ice
+Physical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy does not attack. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy is destroyed if blocked. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor of target enemy is reduced by 5 (to a minimum of 1). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target enemy loses all fortifications and resistances. </t>
+  </si>
+  <si>
+    <t>When activating this unit, you may use multiple different abilities against the same or different targets.</t>
+  </si>
+  <si>
+    <t>2eb8d4</t>
+  </si>
+  <si>
+    <t>2eb8e5</t>
+  </si>
+  <si>
+    <t>2eb8e3</t>
+  </si>
+  <si>
+    <t>2eb8d3</t>
+  </si>
+  <si>
+    <t>2eb8d8</t>
+  </si>
+  <si>
+    <t>2eb8e2</t>
+  </si>
+  <si>
+    <t>2eb8e7</t>
+  </si>
+  <si>
+    <t>2eb8d0</t>
+  </si>
+  <si>
+    <t>2eb8d6</t>
+  </si>
+  <si>
+    <t>2eb8e4</t>
+  </si>
+  <si>
+    <t>2eb8e9</t>
+  </si>
+  <si>
+    <t>Target enemy does not attack this combat. You may target additional enemies: pay 1 move point for the second enemy, pay 2 move point for the third enemy, etc.</t>
   </si>
 </sst>
 </file>
@@ -3589,7 +4056,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3662,21 +4129,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3741,7 +4199,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3762,6 +4226,9 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3771,42 +4238,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4112,9 +4548,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38EE428A-3648-43AA-871D-84443E02FB62}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>54</v>
       </c>
@@ -4139,18 +4575,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="112.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="105.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="14.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="112.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="105.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -4170,7 +4606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
@@ -4190,7 +4626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
@@ -4210,7 +4646,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
@@ -4230,7 +4666,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
@@ -4250,7 +4686,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
         <v>3</v>
       </c>
@@ -4270,7 +4706,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
         <v>3</v>
       </c>
@@ -4290,7 +4726,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>3</v>
       </c>
@@ -4310,7 +4746,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>3</v>
       </c>
@@ -4330,7 +4766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
         <v>3</v>
       </c>
@@ -4350,7 +4786,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
         <v>3</v>
       </c>
@@ -4370,7 +4806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>3</v>
       </c>
@@ -4390,7 +4826,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>3</v>
       </c>
@@ -4410,7 +4846,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>3</v>
       </c>
@@ -4430,7 +4866,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>3</v>
       </c>
@@ -4450,7 +4886,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>3</v>
       </c>
@@ -4470,7 +4906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>3</v>
       </c>
@@ -4490,7 +4926,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>3</v>
       </c>
@@ -4510,7 +4946,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>3</v>
       </c>
@@ -4530,7 +4966,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>3</v>
       </c>
@@ -4550,7 +4986,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>3</v>
       </c>
@@ -4570,7 +5006,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>3</v>
       </c>
@@ -4590,7 +5026,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
         <v>3</v>
       </c>
@@ -4610,7 +5046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>3</v>
       </c>
@@ -4630,7 +5066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>3</v>
       </c>
@@ -4650,7 +5086,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>3</v>
       </c>
@@ -4670,7 +5106,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>3</v>
       </c>
@@ -4690,7 +5126,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>3</v>
       </c>
@@ -4710,7 +5146,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
         <v>3</v>
       </c>
@@ -4730,7 +5166,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
         <v>36</v>
       </c>
@@ -4750,7 +5186,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>36</v>
       </c>
@@ -4770,7 +5206,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>36</v>
       </c>
@@ -4790,7 +5226,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>36</v>
       </c>
@@ -4810,7 +5246,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>36</v>
       </c>
@@ -4830,7 +5266,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>36</v>
       </c>
@@ -4850,7 +5286,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>36</v>
       </c>
@@ -4870,7 +5306,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>36</v>
       </c>
@@ -4890,7 +5326,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>36</v>
       </c>
@@ -4910,7 +5346,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>36</v>
       </c>
@@ -4930,7 +5366,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>36</v>
       </c>
@@ -4950,7 +5386,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>36</v>
       </c>
@@ -4970,7 +5406,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
         <v>49</v>
       </c>
@@ -4990,7 +5426,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
         <v>49</v>
       </c>
@@ -5010,7 +5446,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
         <v>49</v>
       </c>
@@ -5030,7 +5466,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
         <v>49</v>
       </c>
@@ -5063,17 +5499,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4487065-31BB-45F2-B223-F2A0D1499038}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="61.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="61.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.85546875" style="37"/>
-    <col min="5" max="5" width="52.28515625" style="37" customWidth="1"/>
-    <col min="6" max="16384" width="61.85546875" style="34"/>
+    <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.88671875" style="23"/>
+    <col min="5" max="5" width="52.33203125" style="23" customWidth="1"/>
+    <col min="6" max="16384" width="61.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>54</v>
       </c>
@@ -5090,336 +5526,364 @@
         <v>792</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="38" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="6" t="s">
         <v>788</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="21" t="s">
         <v>789</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="21" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="38" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="21" t="s">
         <v>793</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="21" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="33" t="s">
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="21" t="s">
         <v>796</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="21" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="33" t="s">
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="22" t="s">
         <v>820</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="22" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="38" t="s">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="6" t="s">
         <v>800</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>823</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="21" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="33" t="s">
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="22" t="s">
         <v>825</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="21" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="33" t="s">
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="21" t="s">
         <v>827</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="21" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="33" t="s">
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="21" t="s">
         <v>829</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="21" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="38" t="s">
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="21" t="s">
         <v>831</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="21" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="38" t="s">
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="21" t="s">
         <v>833</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="21" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="38" t="s">
+    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="6" t="s">
         <v>806</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="21" t="s">
         <v>835</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="21" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="38" t="s">
+      <c r="E13" s="21" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>840</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>807</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>837</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>808</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>839</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>809</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>841</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="33" t="s">
-        <v>810</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>843</v>
-      </c>
-      <c r="E16" s="36" t="s">
+      <c r="C17" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>811</v>
-      </c>
-      <c r="D17" s="36" t="s">
+      <c r="E17" s="21" t="s">
         <v>845</v>
       </c>
-      <c r="E17" s="36" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="D18" s="21" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="33" t="s">
-        <v>812</v>
-      </c>
-      <c r="D18" s="36" t="s">
+      <c r="E18" s="21" t="s">
         <v>847</v>
       </c>
-      <c r="E18" s="36" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D19" s="21" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="33" t="s">
-        <v>813</v>
-      </c>
-      <c r="D19" s="36" t="s">
+      <c r="E19" s="21" t="s">
         <v>849</v>
       </c>
-      <c r="E19" s="36" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="33" t="s">
-        <v>814</v>
-      </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="21" t="s">
         <v>851</v>
       </c>
-      <c r="E20" s="36" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="33" t="s">
-        <v>815</v>
-      </c>
-      <c r="D21" s="36" t="s">
+      <c r="E21" s="21" t="s">
         <v>853</v>
       </c>
-      <c r="E21" s="36" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="33" t="s">
-        <v>816</v>
-      </c>
-      <c r="D22" s="36" t="s">
+      <c r="E22" s="21" t="s">
         <v>855</v>
       </c>
-      <c r="E22" s="36" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="33" t="s">
-        <v>817</v>
-      </c>
-      <c r="D23" s="40" t="s">
+      <c r="E23" s="21" t="s">
         <v>857</v>
       </c>
-      <c r="E23" s="36" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="33" t="s">
-        <v>818</v>
-      </c>
-      <c r="D24" s="36" t="s">
+      <c r="E24" s="21" t="s">
         <v>859</v>
       </c>
-      <c r="E24" s="36" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="33" t="s">
-        <v>819</v>
-      </c>
-      <c r="D25" s="36" t="s">
+      <c r="E25" s="21" t="s">
         <v>861</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -5430,16 +5894,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1518E3E-453A-4819-AA88-E10B951A9C6F}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="40.85546875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="5.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="40.88671875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>54</v>
       </c>
@@ -5450,307 +5914,307 @@
         <v>1</v>
       </c>
       <c r="D1" s="19" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>889</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="42" t="s">
+      <c r="D3" s="12" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="C4" s="12" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="42" t="s">
+      <c r="D4" s="12" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>893</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="42" t="s">
+      <c r="D5" s="12" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="42" t="s">
+      <c r="D6" s="12" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>897</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="42" t="s">
+      <c r="D7" s="12" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>899</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C8" s="12" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="42" t="s">
+      <c r="D8" s="12" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>901</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="C9" s="12" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="42" t="s">
+      <c r="D9" s="12" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>903</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="42" t="s">
+      <c r="D10" s="12" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>905</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C11" s="12" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="42" t="s">
+      <c r="D11" s="12" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="42" t="s">
+      <c r="D12" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>909</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="42" t="s">
+      <c r="D13" s="12" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>911</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="42" t="s">
+      <c r="D14" s="12" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
         <v>876</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>913</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="42" t="s">
+      <c r="D15" s="12" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>915</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="42" t="s">
+      <c r="D16" s="12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>917</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="C17" s="12" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="42" t="s">
+      <c r="D17" s="12" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>919</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C18" s="12" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="42" t="s">
+      <c r="D18" s="12" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>921</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="42" t="s">
+      <c r="D19" s="12" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>923</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="C20" s="12" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="42" t="s">
+      <c r="D20" s="12" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>925</v>
-      </c>
-      <c r="D20" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="42" t="s">
+      <c r="D21" s="12" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>927</v>
-      </c>
-      <c r="D21" s="12" t="s">
+      <c r="C22" s="12" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="42" t="s">
+      <c r="D22" s="12" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12" t="s">
         <v>884</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>929</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="C23" s="12" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="42" t="s">
+      <c r="D23" s="12" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>931</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="C24" s="12" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="42" t="s">
+      <c r="D24" s="12" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12" t="s">
         <v>886</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>933</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="42" t="s">
+      <c r="D25" s="12" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12" t="s">
         <v>887</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>935</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="C26" s="12" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="42" t="s">
-        <v>888</v>
-      </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="12" t="s">
         <v>937</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -5760,238 +6224,1260 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523F47E6-7E6F-4E51-BCA8-02BFAECA2517}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.21875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
+        <v>993</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>995</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>996</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>954</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>949</v>
+      </c>
+      <c r="J1" s="18" t="s">
         <v>955</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>950</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="L1" s="18" t="s">
         <v>956</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="M1" s="18" t="s">
         <v>951</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="N1" s="18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>938</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+    </row>
+    <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="C3" s="14">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14">
+        <v>3</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="12" t="s">
+        <v>953</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="C4" s="14">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="E4" s="14">
+        <v>2</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14" t="s">
+        <v>997</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="K4" s="12" t="s">
         <v>957</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="L4" s="14"/>
+      <c r="M4" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>978</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14">
+        <v>5</v>
+      </c>
+      <c r="E5" s="14">
+        <v>4</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="12" t="s">
+        <v>984</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="C6" s="14">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14">
+        <v>6</v>
+      </c>
+      <c r="E6" s="14">
+        <v>4</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="L6" s="14"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2</v>
+      </c>
+      <c r="D7" s="14">
+        <v>5</v>
+      </c>
+      <c r="E7" s="14">
+        <v>5</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>975</v>
+      </c>
+      <c r="C8" s="14">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14">
+        <v>6</v>
+      </c>
+      <c r="E8" s="14">
+        <v>4</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="12" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14">
+        <v>7</v>
+      </c>
+      <c r="E9" s="14">
+        <v>3</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>998</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>973</v>
+      </c>
+      <c r="C10" s="14">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14">
+        <v>7</v>
+      </c>
+      <c r="E10" s="14">
+        <v>2</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="12" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2</v>
+      </c>
+      <c r="D11" s="14">
+        <v>7</v>
+      </c>
+      <c r="E11" s="14">
+        <v>4</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>971</v>
+      </c>
+      <c r="C12" s="14">
+        <v>2</v>
+      </c>
+      <c r="D12" s="14">
+        <v>7</v>
+      </c>
+      <c r="E12" s="14">
+        <v>4</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14">
+        <v>7</v>
+      </c>
+      <c r="E13" s="14">
+        <v>4</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L13" s="14"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="12" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J14" s="14"/>
+      <c r="K14" s="12" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="12" t="s">
+        <v>1035</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>5</v>
+      </c>
+      <c r="E15" s="14">
+        <v>5</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="J15" s="14"/>
+      <c r="K15" s="12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L15" s="14"/>
+      <c r="M15" s="12" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>6</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J16" s="14"/>
+      <c r="K16" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L16" s="14"/>
+      <c r="M16" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>966</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6</v>
+      </c>
+      <c r="E17" s="14">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="12" t="s">
+        <v>1038</v>
+      </c>
+      <c r="J17" s="14"/>
+      <c r="K17" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L17" s="14"/>
+      <c r="M17" s="12" t="s">
+        <v>1040</v>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="35" t="s">
         <v>939</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+    </row>
+    <row r="19" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>940</v>
+      </c>
+      <c r="C19" s="14">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="14">
+        <v>4</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>998</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="D3" t="s">
-        <v>949</v>
-      </c>
-      <c r="F3" t="s">
-        <v>953</v>
-      </c>
-      <c r="H3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
-        <v>980</v>
-      </c>
-      <c r="D4" t="s">
-        <v>958</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J19" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L19" s="14"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+    </row>
+    <row r="20" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>8</v>
+      </c>
+      <c r="E20" s="14">
+        <v>4</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>998</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L20" s="14"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="C21" s="14">
+        <v>3</v>
+      </c>
+      <c r="D21" s="14">
+        <v>9</v>
+      </c>
+      <c r="E21" s="14">
+        <v>4</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L21" s="14"/>
+      <c r="M21" s="12" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+    </row>
+    <row r="22" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>9</v>
+      </c>
+      <c r="E22" s="14">
+        <v>4</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L22" s="14"/>
+      <c r="M22" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14">
+        <v>8</v>
+      </c>
+      <c r="E23" s="14">
+        <v>6</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+    </row>
+    <row r="24" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="C24" s="14">
+        <v>3</v>
+      </c>
+      <c r="D24" s="14">
+        <v>8</v>
+      </c>
+      <c r="E24" s="14">
+        <v>6</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>965</v>
+      </c>
+      <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
+        <v>9</v>
+      </c>
+      <c r="E25" s="14">
+        <v>4</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+    </row>
+    <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="C26" s="14">
+        <v>4</v>
+      </c>
+      <c r="D26" s="14">
+        <v>12</v>
+      </c>
+      <c r="E26" s="14">
+        <v>5</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J26" s="14"/>
+      <c r="K26" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+    </row>
+    <row r="27" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="C27" s="14">
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
+        <v>11</v>
+      </c>
+      <c r="E27" s="14">
+        <v>7</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J27" s="14"/>
+      <c r="K27" s="12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+    </row>
+    <row r="28" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>964</v>
+      </c>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>9</v>
+      </c>
+      <c r="E28" s="14">
+        <v>6</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L28" s="14"/>
+      <c r="M28" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>963</v>
+      </c>
+      <c r="C29" s="14">
+        <v>3</v>
+      </c>
+      <c r="D29" s="14">
+        <v>9</v>
+      </c>
+      <c r="E29" s="14">
+        <v>3</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="L29" s="14"/>
+      <c r="M29" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="C30" s="14">
+        <v>3</v>
+      </c>
+      <c r="D30" s="14">
+        <v>9</v>
+      </c>
+      <c r="E30" s="14">
+        <v>4</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L30" s="14"/>
+      <c r="M30" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="C31" s="14">
+        <v>3</v>
+      </c>
+      <c r="D31" s="14">
+        <v>9</v>
+      </c>
+      <c r="E31" s="14">
+        <v>4</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L31" s="14"/>
+      <c r="M31" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+    </row>
+    <row r="32" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="C32" s="14">
+        <v>3</v>
+      </c>
+      <c r="D32" s="14">
+        <v>9</v>
+      </c>
+      <c r="E32" s="14">
+        <v>4</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="12" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="M32" s="12" t="s">
+        <v>1099</v>
+      </c>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="32" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="32" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="32" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="32" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="32" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="32" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="32" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="32" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
-        <v>940</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="32" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="32" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="32" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="32" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="32" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="32" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="32" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="32" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="32" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="32" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="32" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="32" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="32" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="32" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="32" t="s">
-        <v>960</v>
+      <c r="C33" s="14">
+        <v>4</v>
+      </c>
+      <c r="D33" s="14">
+        <v>13</v>
+      </c>
+      <c r="E33" s="14">
+        <v>3</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A18:P18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6000,16 +7486,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6CAB4A-A364-4A18-B7EC-71D43CA49563}">
   <dimension ref="A1:D172"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="101.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="97.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="97.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>404</v>
       </c>
@@ -6023,15 +7509,15 @@
         <v>401</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+    </row>
+    <row r="3" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>102</v>
       </c>
@@ -6043,7 +7529,7 @@
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>104</v>
       </c>
@@ -6055,7 +7541,7 @@
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>106</v>
       </c>
@@ -6067,7 +7553,7 @@
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>108</v>
       </c>
@@ -6079,7 +7565,7 @@
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>110</v>
       </c>
@@ -6091,7 +7577,7 @@
       </c>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>112</v>
       </c>
@@ -6103,7 +7589,7 @@
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
@@ -6115,7 +7601,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>116</v>
       </c>
@@ -6127,7 +7613,7 @@
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>118</v>
       </c>
@@ -6141,7 +7627,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>120</v>
       </c>
@@ -6155,7 +7641,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>122</v>
       </c>
@@ -6167,15 +7653,15 @@
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-    </row>
-    <row r="15" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+    </row>
+    <row r="15" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>125</v>
       </c>
@@ -6187,7 +7673,7 @@
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>46187</v>
       </c>
@@ -6199,7 +7685,7 @@
       </c>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>128</v>
       </c>
@@ -6211,7 +7697,7 @@
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>130</v>
       </c>
@@ -6223,7 +7709,7 @@
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>132</v>
       </c>
@@ -6235,7 +7721,7 @@
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>134</v>
       </c>
@@ -6247,7 +7733,7 @@
       </c>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>136</v>
       </c>
@@ -6259,7 +7745,7 @@
       </c>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>405</v>
       </c>
@@ -6271,7 +7757,7 @@
       </c>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>139</v>
       </c>
@@ -6285,7 +7771,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>140</v>
       </c>
@@ -6299,7 +7785,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>676856</v>
       </c>
@@ -6311,15 +7797,15 @@
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-    </row>
-    <row r="27" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+    </row>
+    <row r="27" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>144</v>
       </c>
@@ -6331,7 +7817,7 @@
       </c>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>866002</v>
       </c>
@@ -6343,7 +7829,7 @@
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>147</v>
       </c>
@@ -6355,7 +7841,7 @@
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>149</v>
       </c>
@@ -6367,7 +7853,7 @@
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>151</v>
       </c>
@@ -6379,7 +7865,7 @@
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>153</v>
       </c>
@@ -6391,7 +7877,7 @@
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>155</v>
       </c>
@@ -6403,7 +7889,7 @@
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>157</v>
       </c>
@@ -6415,7 +7901,7 @@
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>171244</v>
       </c>
@@ -6429,7 +7915,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>159</v>
       </c>
@@ -6443,7 +7929,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>161</v>
       </c>
@@ -6455,15 +7941,15 @@
       </c>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-    </row>
-    <row r="39" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
+    </row>
+    <row r="39" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>406</v>
       </c>
@@ -6475,7 +7961,7 @@
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>165</v>
       </c>
@@ -6487,7 +7973,7 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>167</v>
       </c>
@@ -6499,7 +7985,7 @@
       </c>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>169</v>
       </c>
@@ -6511,7 +7997,7 @@
       </c>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>171</v>
       </c>
@@ -6523,7 +8009,7 @@
       </c>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>173</v>
       </c>
@@ -6535,7 +8021,7 @@
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>175</v>
       </c>
@@ -6547,7 +8033,7 @@
       </c>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>177</v>
       </c>
@@ -6559,7 +8045,7 @@
       </c>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>179</v>
       </c>
@@ -6573,7 +8059,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>180</v>
       </c>
@@ -6587,7 +8073,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>182</v>
       </c>
@@ -6599,15 +8085,15 @@
       </c>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="25"/>
-    </row>
-    <row r="51" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27"/>
+    </row>
+    <row r="51" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>210835</v>
       </c>
@@ -6619,7 +8105,7 @@
       </c>
       <c r="D51" s="6"/>
     </row>
-    <row r="52" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>186</v>
       </c>
@@ -6631,7 +8117,7 @@
       </c>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>188</v>
       </c>
@@ -6643,7 +8129,7 @@
       </c>
       <c r="D53" s="6"/>
     </row>
-    <row r="54" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>190</v>
       </c>
@@ -6655,7 +8141,7 @@
       </c>
       <c r="D54" s="6"/>
     </row>
-    <row r="55" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>192</v>
       </c>
@@ -6667,7 +8153,7 @@
       </c>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>194</v>
       </c>
@@ -6679,7 +8165,7 @@
       </c>
       <c r="D56" s="6"/>
     </row>
-    <row r="57" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>196</v>
       </c>
@@ -6691,7 +8177,7 @@
       </c>
       <c r="D57" s="6"/>
     </row>
-    <row r="58" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>198</v>
       </c>
@@ -6703,7 +8189,7 @@
       </c>
       <c r="D58" s="6"/>
     </row>
-    <row r="59" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>200</v>
       </c>
@@ -6717,7 +8203,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>564392</v>
       </c>
@@ -6731,7 +8217,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>202</v>
       </c>
@@ -6743,15 +8229,15 @@
       </c>
       <c r="D61" s="6"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="25"/>
-    </row>
-    <row r="63" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="27"/>
+    </row>
+    <row r="63" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>205</v>
       </c>
@@ -6763,7 +8249,7 @@
       </c>
       <c r="D63" s="6"/>
     </row>
-    <row r="64" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>207</v>
       </c>
@@ -6775,7 +8261,7 @@
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>209</v>
       </c>
@@ -6787,7 +8273,7 @@
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>211</v>
       </c>
@@ -6799,7 +8285,7 @@
       </c>
       <c r="D66" s="6"/>
     </row>
-    <row r="67" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>213</v>
       </c>
@@ -6811,7 +8297,7 @@
       </c>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>893537</v>
       </c>
@@ -6823,7 +8309,7 @@
       </c>
       <c r="D68" s="6"/>
     </row>
-    <row r="69" spans="1:4" ht="165.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="179.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>216</v>
       </c>
@@ -6835,7 +8321,7 @@
       </c>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>218</v>
       </c>
@@ -6847,7 +8333,7 @@
       </c>
       <c r="D70" s="6"/>
     </row>
-    <row r="71" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>220</v>
       </c>
@@ -6861,7 +8347,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>222</v>
       </c>
@@ -6875,7 +8361,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="138" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>958209</v>
       </c>
@@ -6887,15 +8373,15 @@
       </c>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="23" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="25"/>
-    </row>
-    <row r="75" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="27"/>
+    </row>
+    <row r="75" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>122015</v>
       </c>
@@ -6907,7 +8393,7 @@
       </c>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>227</v>
       </c>
@@ -6919,7 +8405,7 @@
       </c>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>229</v>
       </c>
@@ -6931,7 +8417,7 @@
       </c>
       <c r="D77" s="6"/>
     </row>
-    <row r="78" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>231</v>
       </c>
@@ -6943,7 +8429,7 @@
       </c>
       <c r="D78" s="6"/>
     </row>
-    <row r="79" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>233</v>
       </c>
@@ -6955,7 +8441,7 @@
       </c>
       <c r="D79" s="6"/>
     </row>
-    <row r="80" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>235</v>
       </c>
@@ -6967,7 +8453,7 @@
       </c>
       <c r="D80" s="6"/>
     </row>
-    <row r="81" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>237</v>
       </c>
@@ -6979,7 +8465,7 @@
       </c>
       <c r="D81" s="6"/>
     </row>
-    <row r="82" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>239</v>
       </c>
@@ -6991,7 +8477,7 @@
       </c>
       <c r="D82" s="6"/>
     </row>
-    <row r="83" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>241</v>
       </c>
@@ -7005,7 +8491,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>242</v>
       </c>
@@ -7019,7 +8505,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>244</v>
       </c>
@@ -7031,15 +8517,15 @@
       </c>
       <c r="D85" s="6"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="23" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
-      <c r="D86" s="25"/>
-    </row>
-    <row r="87" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="27"/>
+    </row>
+    <row r="87" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>380</v>
       </c>
@@ -7051,7 +8537,7 @@
       </c>
       <c r="D87" s="6"/>
     </row>
-    <row r="88" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>382</v>
       </c>
@@ -7063,7 +8549,7 @@
       </c>
       <c r="D88" s="6"/>
     </row>
-    <row r="89" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>384</v>
       </c>
@@ -7075,7 +8561,7 @@
       </c>
       <c r="D89" s="6"/>
     </row>
-    <row r="90" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>386</v>
       </c>
@@ -7087,7 +8573,7 @@
       </c>
       <c r="D90" s="6"/>
     </row>
-    <row r="91" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>6.9399999999999996E+29</v>
       </c>
@@ -7099,7 +8585,7 @@
       </c>
       <c r="D91" s="6"/>
     </row>
-    <row r="92" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>389</v>
       </c>
@@ -7111,7 +8597,7 @@
       </c>
       <c r="D92" s="6"/>
     </row>
-    <row r="93" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>391</v>
       </c>
@@ -7123,7 +8609,7 @@
       </c>
       <c r="D93" s="6"/>
     </row>
-    <row r="94" spans="1:4" ht="153" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>393</v>
       </c>
@@ -7135,7 +8621,7 @@
       </c>
       <c r="D94" s="6"/>
     </row>
-    <row r="95" spans="1:4" ht="191.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="207" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>395</v>
       </c>
@@ -7147,7 +8633,7 @@
       </c>
       <c r="D95" s="6"/>
     </row>
-    <row r="96" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>397</v>
       </c>
@@ -7161,7 +8647,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>399</v>
       </c>
@@ -7173,23 +8659,23 @@
       </c>
       <c r="D97" s="6"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="26" t="s">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="28" t="s">
         <v>407</v>
       </c>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
-      <c r="D98" s="28"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="23" t="s">
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="30"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="B99" s="24"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="25"/>
-    </row>
-    <row r="100" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="27"/>
+    </row>
+    <row r="100" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>247</v>
       </c>
@@ -7201,7 +8687,7 @@
       </c>
       <c r="D100" s="6"/>
     </row>
-    <row r="101" spans="1:4" ht="153" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>249</v>
       </c>
@@ -7213,7 +8699,7 @@
       </c>
       <c r="D101" s="6"/>
     </row>
-    <row r="102" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>251</v>
       </c>
@@ -7225,7 +8711,7 @@
       </c>
       <c r="D102" s="6"/>
     </row>
-    <row r="103" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>253</v>
       </c>
@@ -7237,7 +8723,7 @@
       </c>
       <c r="D103" s="6"/>
     </row>
-    <row r="104" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>38787</v>
       </c>
@@ -7249,7 +8735,7 @@
       </c>
       <c r="D104" s="6"/>
     </row>
-    <row r="105" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>929377</v>
       </c>
@@ -7261,7 +8747,7 @@
       </c>
       <c r="D105" s="6"/>
     </row>
-    <row r="106" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>257</v>
       </c>
@@ -7273,7 +8759,7 @@
       </c>
       <c r="D106" s="6"/>
     </row>
-    <row r="107" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>259</v>
       </c>
@@ -7285,7 +8771,7 @@
       </c>
       <c r="D107" s="6"/>
     </row>
-    <row r="108" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>261</v>
       </c>
@@ -7297,7 +8783,7 @@
       </c>
       <c r="D108" s="6"/>
     </row>
-    <row r="109" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>263</v>
       </c>
@@ -7311,7 +8797,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>335290</v>
       </c>
@@ -7323,15 +8809,15 @@
       </c>
       <c r="D110" s="6"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
-      <c r="D111" s="25"/>
-    </row>
-    <row r="112" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="27"/>
+    </row>
+    <row r="112" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>267</v>
       </c>
@@ -7343,7 +8829,7 @@
       </c>
       <c r="D112" s="6"/>
     </row>
-    <row r="113" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>269</v>
       </c>
@@ -7355,7 +8841,7 @@
       </c>
       <c r="D113" s="6"/>
     </row>
-    <row r="114" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>271</v>
       </c>
@@ -7367,7 +8853,7 @@
       </c>
       <c r="D114" s="6"/>
     </row>
-    <row r="115" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>273</v>
       </c>
@@ -7379,7 +8865,7 @@
       </c>
       <c r="D115" s="6"/>
     </row>
-    <row r="116" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>275</v>
       </c>
@@ -7391,7 +8877,7 @@
       </c>
       <c r="D116" s="6"/>
     </row>
-    <row r="117" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>277</v>
       </c>
@@ -7403,7 +8889,7 @@
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>278</v>
       </c>
@@ -7415,7 +8901,7 @@
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>280</v>
       </c>
@@ -7427,7 +8913,7 @@
       </c>
       <c r="D119" s="6"/>
     </row>
-    <row r="120" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>282</v>
       </c>
@@ -7439,7 +8925,7 @@
       </c>
       <c r="D120" s="6"/>
     </row>
-    <row r="121" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>284</v>
       </c>
@@ -7453,7 +8939,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>286</v>
       </c>
@@ -7465,15 +8951,15 @@
       </c>
       <c r="D122" s="6"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="23" t="s">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="B123" s="24"/>
-      <c r="C123" s="24"/>
-      <c r="D123" s="25"/>
-    </row>
-    <row r="124" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="27"/>
+    </row>
+    <row r="124" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>289</v>
       </c>
@@ -7485,7 +8971,7 @@
       </c>
       <c r="D124" s="6"/>
     </row>
-    <row r="125" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="138" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>291</v>
       </c>
@@ -7497,7 +8983,7 @@
       </c>
       <c r="D125" s="6"/>
     </row>
-    <row r="126" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>293</v>
       </c>
@@ -7509,7 +8995,7 @@
       </c>
       <c r="D126" s="6"/>
     </row>
-    <row r="127" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>295</v>
       </c>
@@ -7521,7 +9007,7 @@
       </c>
       <c r="D127" s="6"/>
     </row>
-    <row r="128" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>297</v>
       </c>
@@ -7533,7 +9019,7 @@
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>299</v>
       </c>
@@ -7543,7 +9029,7 @@
       <c r="C129" s="6"/>
       <c r="D129" s="6"/>
     </row>
-    <row r="130" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>301</v>
       </c>
@@ -7553,7 +9039,7 @@
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>303</v>
       </c>
@@ -7565,7 +9051,7 @@
       </c>
       <c r="D131" s="6"/>
     </row>
-    <row r="132" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>305</v>
       </c>
@@ -7577,7 +9063,7 @@
       </c>
       <c r="D132" s="6"/>
     </row>
-    <row r="133" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>107400</v>
       </c>
@@ -7589,7 +9075,7 @@
       </c>
       <c r="D133" s="6"/>
     </row>
-    <row r="134" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>308</v>
       </c>
@@ -7601,7 +9087,7 @@
       </c>
       <c r="D134" s="6"/>
     </row>
-    <row r="135" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>676855</v>
       </c>
@@ -7613,15 +9099,15 @@
       </c>
       <c r="D135" s="6"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="23" t="s">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="B136" s="24"/>
-      <c r="C136" s="24"/>
-      <c r="D136" s="25"/>
-    </row>
-    <row r="137" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
+      <c r="D136" s="27"/>
+    </row>
+    <row r="137" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>312</v>
       </c>
@@ -7633,7 +9119,7 @@
       </c>
       <c r="D137" s="6"/>
     </row>
-    <row r="138" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>314</v>
       </c>
@@ -7645,7 +9131,7 @@
       </c>
       <c r="D138" s="6"/>
     </row>
-    <row r="139" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>316</v>
       </c>
@@ -7657,7 +9143,7 @@
       </c>
       <c r="D139" s="6"/>
     </row>
-    <row r="140" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>318</v>
       </c>
@@ -7669,7 +9155,7 @@
       </c>
       <c r="D140" s="6"/>
     </row>
-    <row r="141" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>320</v>
       </c>
@@ -7681,7 +9167,7 @@
       </c>
       <c r="D141" s="6"/>
     </row>
-    <row r="142" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>322</v>
       </c>
@@ -7693,7 +9179,7 @@
       </c>
       <c r="D142" s="6"/>
     </row>
-    <row r="143" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>324</v>
       </c>
@@ -7705,7 +9191,7 @@
       </c>
       <c r="D143" s="6"/>
     </row>
-    <row r="144" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>933090</v>
       </c>
@@ -7717,7 +9203,7 @@
       </c>
       <c r="D144" s="6"/>
     </row>
-    <row r="145" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>327</v>
       </c>
@@ -7729,7 +9215,7 @@
       </c>
       <c r="D145" s="6"/>
     </row>
-    <row r="146" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>329</v>
       </c>
@@ -7741,7 +9227,7 @@
       </c>
       <c r="D146" s="6"/>
     </row>
-    <row r="147" spans="1:4" ht="191.25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="207" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>331</v>
       </c>
@@ -7753,7 +9239,7 @@
       </c>
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="1:4" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="138" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>333</v>
       </c>
@@ -7765,15 +9251,15 @@
       </c>
       <c r="D148" s="6"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="23" t="s">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="B149" s="24"/>
-      <c r="C149" s="24"/>
-      <c r="D149" s="25"/>
-    </row>
-    <row r="150" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="27"/>
+    </row>
+    <row r="150" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>336</v>
       </c>
@@ -7785,7 +9271,7 @@
       </c>
       <c r="D150" s="6"/>
     </row>
-    <row r="151" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>338</v>
       </c>
@@ -7797,7 +9283,7 @@
       </c>
       <c r="D151" s="6"/>
     </row>
-    <row r="152" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>340</v>
       </c>
@@ -7809,7 +9295,7 @@
       </c>
       <c r="D152" s="6"/>
     </row>
-    <row r="153" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>342</v>
       </c>
@@ -7821,7 +9307,7 @@
       </c>
       <c r="D153" s="6"/>
     </row>
-    <row r="154" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>344</v>
       </c>
@@ -7833,7 +9319,7 @@
       </c>
       <c r="D154" s="6"/>
     </row>
-    <row r="155" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>346</v>
       </c>
@@ -7845,7 +9331,7 @@
       </c>
       <c r="D155" s="6"/>
     </row>
-    <row r="156" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>62555</v>
       </c>
@@ -7857,7 +9343,7 @@
       </c>
       <c r="D156" s="6"/>
     </row>
-    <row r="157" spans="1:4" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>349</v>
       </c>
@@ -7869,7 +9355,7 @@
       </c>
       <c r="D157" s="6"/>
     </row>
-    <row r="158" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>351</v>
       </c>
@@ -7881,7 +9367,7 @@
       </c>
       <c r="D158" s="6"/>
     </row>
-    <row r="159" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>353</v>
       </c>
@@ -7895,7 +9381,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
         <v>408</v>
       </c>
@@ -7907,15 +9393,15 @@
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="23" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="24"/>
-      <c r="C161" s="24"/>
-      <c r="D161" s="25"/>
-    </row>
-    <row r="162" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B161" s="26"/>
+      <c r="C161" s="26"/>
+      <c r="D161" s="27"/>
+    </row>
+    <row r="162" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>357</v>
       </c>
@@ -7927,7 +9413,7 @@
       </c>
       <c r="D162" s="6"/>
     </row>
-    <row r="163" spans="1:4" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>359</v>
       </c>
@@ -7939,7 +9425,7 @@
       </c>
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>361</v>
       </c>
@@ -7951,7 +9437,7 @@
       </c>
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>363</v>
       </c>
@@ -7963,7 +9449,7 @@
       </c>
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>365</v>
       </c>
@@ -7975,7 +9461,7 @@
       </c>
       <c r="D166" s="6"/>
     </row>
-    <row r="167" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>367</v>
       </c>
@@ -7987,7 +9473,7 @@
       </c>
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="1:4" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>369</v>
       </c>
@@ -7999,7 +9485,7 @@
       </c>
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="1:4" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>371</v>
       </c>
@@ -8011,7 +9497,7 @@
       </c>
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>373</v>
       </c>
@@ -8023,7 +9509,7 @@
       </c>
       <c r="D170" s="6"/>
     </row>
-    <row r="171" spans="1:4" ht="102" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>375</v>
       </c>
@@ -8037,7 +9523,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>377</v>
       </c>
@@ -8051,6 +9537,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A86:D86"/>
     <mergeCell ref="A98:D98"/>
@@ -8061,11 +9552,6 @@
     <mergeCell ref="A111:D111"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A50:D50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8075,15 +9561,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BFD584-66AF-44F3-9DD5-44943E29E62D}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="103.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="103.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="164.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="103.85546875" style="1"/>
+    <col min="1" max="1" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="164.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="103.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>609</v>
       </c>
@@ -8094,14 +9580,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
         <v>593</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+    </row>
+    <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>619</v>
       </c>
@@ -8112,7 +9598,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>618</v>
       </c>
@@ -8123,7 +9609,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>616</v>
       </c>
@@ -8134,7 +9620,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>620</v>
       </c>
@@ -8145,7 +9631,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>617</v>
       </c>
@@ -8156,7 +9642,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>621</v>
       </c>
@@ -8167,14 +9653,14 @@
         <v>639</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-    </row>
-    <row r="10" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+    </row>
+    <row r="10" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>615</v>
       </c>
@@ -8185,7 +9671,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>610</v>
       </c>
@@ -8196,7 +9682,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>611</v>
       </c>
@@ -8207,7 +9693,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>612</v>
       </c>
@@ -8218,7 +9704,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>613</v>
       </c>
@@ -8229,7 +9715,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>614</v>
       </c>
@@ -8240,14 +9726,14 @@
         <v>645</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
         <v>595</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-    </row>
-    <row r="17" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+    </row>
+    <row r="17" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>627</v>
       </c>
@@ -8258,7 +9744,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>624</v>
       </c>
@@ -8269,7 +9755,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>622</v>
       </c>
@@ -8280,7 +9766,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>623</v>
       </c>
@@ -8291,7 +9777,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>626</v>
       </c>
@@ -8302,7 +9788,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>625</v>
       </c>
@@ -8313,14 +9799,14 @@
         <v>651</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="33" t="s">
         <v>596</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-    </row>
-    <row r="24" spans="1:3" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+    </row>
+    <row r="24" spans="1:3" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>628</v>
       </c>
@@ -8331,7 +9817,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>633</v>
       </c>
@@ -8342,7 +9828,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>631</v>
       </c>
@@ -8353,7 +9839,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>632</v>
       </c>
@@ -8364,7 +9850,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>630</v>
       </c>
@@ -8375,7 +9861,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>629</v>
       </c>
@@ -8400,20 +9886,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA0F03E-4077-4D5A-9A57-C44D6F7CF78F}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="3"/>
+    <col min="1" max="1" width="18.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>659</v>
       </c>
-      <c r="B1" s="31"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="34"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>661</v>
       </c>
@@ -8421,7 +9907,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>663</v>
       </c>
@@ -8429,7 +9915,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>664</v>
       </c>
@@ -8437,7 +9923,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>667</v>
       </c>
@@ -8445,7 +9931,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>669</v>
       </c>
@@ -8453,7 +9939,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>670</v>
       </c>
@@ -8461,7 +9947,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>673</v>
       </c>
@@ -8469,13 +9955,13 @@
         <v>672</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
         <v>658</v>
       </c>
-      <c r="B9" s="30"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="33"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>674</v>
       </c>
@@ -8483,7 +9969,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>676</v>
       </c>
@@ -8491,7 +9977,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>678</v>
       </c>
@@ -8499,7 +9985,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>680</v>
       </c>
@@ -8507,7 +9993,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>682</v>
       </c>
@@ -8515,7 +10001,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>683</v>
       </c>
@@ -8523,7 +10009,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>685</v>
       </c>
@@ -8531,7 +10017,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>687</v>
       </c>
@@ -8539,7 +10025,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>689</v>
       </c>
@@ -8547,7 +10033,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>691</v>
       </c>
@@ -8555,7 +10041,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>693</v>
       </c>

--- a/Rules/Mage Knight Card and Skill texts .xlsx
+++ b/Rules/Mage Knight Card and Skill texts .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18c549927b9fc512/Board Games/Mage Knight/TTS/Lua Code/Mage_Knight_Highly_Scripted/Rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{34FC8D39-88EA-4E94-97D8-6F4E26FD2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{244E99E0-54D9-4CC1-9F7F-322150D79929}"/>
+  <xr:revisionPtr revIDLastSave="645" documentId="13_ncr:1_{34FC8D39-88EA-4E94-97D8-6F4E26FD2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E95CCC8D-27BA-408E-AA4A-690B0DACBA43}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Starting Cards" sheetId="9" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="1208">
   <si>
     <t>Set</t>
   </si>
@@ -3216,9 +3216,6 @@
 During the block phase of combat, you may spend this unit to cancel one attack. If you do, fame +1. </t>
   </si>
   <si>
-    <t xml:space="preserve">Skip the block and damage assigning phases of this combat. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Assign this to a unit you control.
 The assigned unit gets armor +1, fire resistance and ice resistance. </t>
   </si>
@@ -3265,14 +3262,6 @@
 Enemies lose physical resistance this turn. Fame +1 for each enemy you defeat this turn. </t>
   </si>
   <si>
-    <t xml:space="preserve">Siege Attack 6.
-Roll a mana die. If you roll black or red, you get a Wound. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siege Attack 6.
-You may add up to +6 to this Siege Attack. For each +1 you added roll a mana die. You get a Wound for each black or red rolled. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Heal 2.
 Fame +1 for each point of Healing provided by this card you spend this turn. </t>
   </si>
@@ -3325,14 +3314,6 @@
   </si>
   <si>
     <t xml:space="preserve">Gain Fame +2.  Recruit any one Unit from the Units offer for free.  (If you are at your Command limit, you must disband one of your units first.) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assign this to a unit you control.
-Once a Round, when the Unit is about to get wounded, flip this card to ignore the Wound and any additional effects from it.  The Unit can still only be assigned damage once each combat. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anytime except during combat:
-Heal all of your Units completely. </t>
   </si>
   <si>
     <t xml:space="preserve">Attack 3.  For one enemy defeated by this attack gain one crystal to your inventory. It may be red if the enemy had Fire Resistance, blue if it had Ice Resistance, green if it had Physical Resistance.  You may always choose white. </t>
@@ -3369,12 +3350,6 @@
     <t xml:space="preserve">Discard a card of any color.  Use the stronger effect of a Spell of the same color from the Spells offer without paying its mana cost.  You may do so even during the Day. </t>
   </si>
   <si>
-    <t>Remove and reveal the top card of the Artifacts deck. This turn, you may use Mysterious Box as if it was that Artifact. If you do then Fame +1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the end of the turn: put the revealed Artifact on the bottom of the Artifacts deck; if you did not use Mysterious Box then put it back in your hand; if you placed it on an unit as a banner then discard it. </t>
-  </si>
-  <si>
     <t>Silver Units</t>
   </si>
   <si>
@@ -3972,6 +3947,315 @@
   </si>
   <si>
     <t>Target enemy does not attack this combat. You may target additional enemies: pay 1 move point for the second enemy, pay 2 move point for the third enemy, etc.</t>
+  </si>
+  <si>
+    <t>2eb8d1</t>
+  </si>
+  <si>
+    <t>2eb8d7</t>
+  </si>
+  <si>
+    <t>2eb8e0</t>
+  </si>
+  <si>
+    <t>2eb8e8</t>
+  </si>
+  <si>
+    <t>2eb8d2</t>
+  </si>
+  <si>
+    <t>2eb8f4</t>
+  </si>
+  <si>
+    <t>8907d7</t>
+  </si>
+  <si>
+    <t>2eb8f5</t>
+  </si>
+  <si>
+    <t>2eb8f3</t>
+  </si>
+  <si>
+    <t>2eb8e6</t>
+  </si>
+  <si>
+    <t>2eb8e1</t>
+  </si>
+  <si>
+    <t>47e71c</t>
+  </si>
+  <si>
+    <t>2eb8d9</t>
+  </si>
+  <si>
+    <t>7d608f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign this to a unit you control. Once a Round, when the Unit is about to get wounded, flip this card to ignore the Wound and any additional effects from it.  The Unit can still only be assigned damage once each combat. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anytime except during combat:
+Heal all of your Units completely. </t>
+  </si>
+  <si>
+    <t>98681f</t>
+  </si>
+  <si>
+    <t>085e68</t>
+  </si>
+  <si>
+    <t>085e66</t>
+  </si>
+  <si>
+    <t>085e67</t>
+  </si>
+  <si>
+    <t>085e63</t>
+  </si>
+  <si>
+    <t>085e64</t>
+  </si>
+  <si>
+    <t>085e65</t>
+  </si>
+  <si>
+    <t>085e69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove and reveal the top card of the Artifacts deck. This turn, you may use Mysterious Box as if it was that Artifact. If you do then Fame +1.
+At the end of the turn: put the revealed Artifact on the bottom of the Artifacts deck; if you did not use Mysterious Box then put it back in your hand; if you placed it on an unit as a banner then discard it. </t>
+  </si>
+  <si>
+    <t>085e59</t>
+  </si>
+  <si>
+    <t>085e56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege Attack 5.
+Roll a mana die. If you roll black or red, you get a Wound. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siege Attack 5.
+You may add up to +5 to this Siege Attack. For each +1 you added roll a mana die. You get a Wound for each black or red rolled. </t>
+  </si>
+  <si>
+    <t>085e55</t>
+  </si>
+  <si>
+    <t>085e57</t>
+  </si>
+  <si>
+    <t>085e61</t>
+  </si>
+  <si>
+    <t>085e62</t>
+  </si>
+  <si>
+    <t>085e58</t>
+  </si>
+  <si>
+    <t>085e60</t>
+  </si>
+  <si>
+    <t>085e50</t>
+  </si>
+  <si>
+    <t>df2eae</t>
+  </si>
+  <si>
+    <t>7b9ec1</t>
+  </si>
+  <si>
+    <t>Up to 3 enemies do not attack this combat.</t>
+  </si>
+  <si>
+    <t>6b4654</t>
+  </si>
+  <si>
+    <t>085e52</t>
+  </si>
+  <si>
+    <t>085e51</t>
+  </si>
+  <si>
+    <t>085e54</t>
+  </si>
+  <si>
+    <t>085e53</t>
+  </si>
+  <si>
+    <t>dea60c</t>
+  </si>
+  <si>
+    <t>Tranquility</t>
+  </si>
+  <si>
+    <t>Heal 1 or draw a card.</t>
+  </si>
+  <si>
+    <t>Heal 2 or draw two cards.</t>
+  </si>
+  <si>
+    <t>Concentration</t>
+  </si>
+  <si>
+    <t>Gain a blue, white or red mana token.</t>
+  </si>
+  <si>
+    <t>When you play this play another Action card with it. Get the stronger effect of that card for free. If that effect gives you move, Influence, Block, or any type of Attack, get that amount plus 2.</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Move 4</t>
+  </si>
+  <si>
+    <t>Infamous Reprisals</t>
+  </si>
+  <si>
+    <t>Mevok</t>
+  </si>
+  <si>
+    <t>Mana Draw</t>
+  </si>
+  <si>
+    <t>You can use one additional mana die from the Source this turn.</t>
+  </si>
+  <si>
+    <t>Take a mana die from the Source and set it to any color except gold. Gain two mana tokens of that color. Do not reroll this die when you return it to the source.</t>
+  </si>
+  <si>
+    <t>Swiftness</t>
+  </si>
+  <si>
+    <t>Determination</t>
+  </si>
+  <si>
+    <t>Block 5</t>
+  </si>
+  <si>
+    <t>Crystalize</t>
+  </si>
+  <si>
+    <t>When you play this, also pay one mana of a basic color. Gain a crystal of that color to your Inventory.</t>
+  </si>
+  <si>
+    <t>Gain a crystal of any color to your Inventory.</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>Improvisation</t>
+  </si>
+  <si>
+    <t>Discard another card from your hand to get Move 5, Influence 5, Attack 5 or Block 5.</t>
+  </si>
+  <si>
+    <t>Discard another card from your hand to get Move 3, Influence 3, Attack 3 or Block 3.</t>
+  </si>
+  <si>
+    <t>Threaten</t>
+  </si>
+  <si>
+    <t>Influence 5.
+Reputaion -1.</t>
+  </si>
+  <si>
+    <t>ba5561</t>
+  </si>
+  <si>
+    <t>Undead Horde</t>
+  </si>
+  <si>
+    <t>Rage</t>
+  </si>
+  <si>
+    <t>Attack 4</t>
+  </si>
+  <si>
+    <t>Mage Knight</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>40422e</t>
+  </si>
+  <si>
+    <t>Hidden River</t>
+  </si>
+  <si>
+    <t>Move 2. Move cost of a single Forest is reduced by 2 to a minimum of 1. If you move through two Forests this turn, gain a blue mana token.</t>
+  </si>
+  <si>
+    <t>Move 4. Move cost of a single Forest is reduced by 2 to a minimum of 1. If you move through two Forests this turn, gain a blue Crystal.</t>
+  </si>
+  <si>
+    <t>bfc394
+187cd2</t>
+  </si>
+  <si>
+    <t>71a74a
+c48176</t>
+  </si>
+  <si>
+    <t>3cfeb6
+98441e
+63076d</t>
+  </si>
+  <si>
+    <t>9a67a9
+124af4</t>
+  </si>
+  <si>
+    <t>1a5a80</t>
+  </si>
+  <si>
+    <t>Duscenia</t>
+  </si>
+  <si>
+    <t>Play 2 Wounds as sideways cards for increasing the total effect by 1 then throe away one of those wounds, Heal 2 (1 Heal may be used on your Discard Pile), or gain a green crystal.</t>
+  </si>
+  <si>
+    <t>Play 1 Wound as a sideways card for double the effect then discard it, Heal 1 (may be used on your Discard Pile), or gain a green mana token.</t>
+  </si>
+  <si>
+    <t>29fa1e
+92aed4
+4c5881
+d890d8</t>
+  </si>
+  <si>
+    <t>0cdfcd
+2c15ec
+d90f22
+64b818</t>
+  </si>
+  <si>
+    <t>42adeb</t>
+  </si>
+  <si>
+    <t>Promise</t>
+  </si>
+  <si>
+    <t>d619c6
+bbd990</t>
+  </si>
+  <si>
+    <t>c4ea63
+690015</t>
+  </si>
+  <si>
+    <t>4a2863
+5c9d35</t>
+  </si>
+  <si>
+    <t>1c58fe
+731725
+78d7fc</t>
   </si>
 </sst>
 </file>
@@ -4134,7 +4418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4208,6 +4492,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4226,9 +4519,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4238,10 +4528,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4547,24 +4834,355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38EE428A-3648-43AA-871D-84443E02FB62}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="21.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.88671875" style="24"/>
+    <col min="2" max="2" width="7" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="56" style="24" customWidth="1"/>
+    <col min="7" max="16384" width="21.88671875" style="24"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>945</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>945</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B15" s="14">
+        <v>585526</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>1198</v>
       </c>
     </row>
   </sheetData>
@@ -5498,391 +6116,515 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4487065-31BB-45F2-B223-F2A0D1499038}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="61.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.88671875" style="23"/>
-    <col min="5" max="5" width="52.33203125" style="23" customWidth="1"/>
-    <col min="6" max="16384" width="61.88671875" style="1"/>
+    <col min="1" max="1" width="14.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.88671875" style="23"/>
+    <col min="6" max="6" width="52.33203125" style="23" customWidth="1"/>
+    <col min="7" max="16384" width="61.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>791</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>822</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>793</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>796</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>820</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>831</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>833</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>836</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>840</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C16" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>844</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>788</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>789</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="D18" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>793</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="D19" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>848</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>796</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>820</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="D20" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>850</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>852</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>823</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="D22" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>854</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>825</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="D23" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>856</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>827</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>829</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>831</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>833</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>806</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>835</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="D24" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>858</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>807</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>836</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>808</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>838</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>840</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>842</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>844</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>846</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>848</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="6" t="s">
-        <v>814</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>850</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="6" t="s">
-        <v>815</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>852</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>854</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>856</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>858</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="E25" s="21" t="s">
         <v>860</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="21" t="s">
         <v>861</v>
       </c>
     </row>
@@ -5893,329 +6635,456 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1518E3E-453A-4819-AA88-E10B951A9C6F}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="40.88671875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="3"/>
+    <col min="1" max="1" width="14.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>791</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12" t="s">
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12" t="s">
-        <v>865</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="D4" s="12" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
-        <v>866</v>
-      </c>
-      <c r="C5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="D5" s="12" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
-        <v>867</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="D6" s="12" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
-        <v>868</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="D7" s="12" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12" t="s">
-        <v>869</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>900</v>
       </c>
-      <c r="D8" s="12" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12" t="s">
-        <v>870</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="D9" s="12" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12" t="s">
-        <v>871</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="D10" s="12" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
-        <v>872</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="D11" s="12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
-        <v>873</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="E13" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="D12" s="12" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12" t="s">
-        <v>874</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>910</v>
       </c>
-      <c r="D13" s="12" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12" t="s">
-        <v>875</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="E15" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="D14" s="12" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
-        <v>876</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="D15" s="12" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12" t="s">
-        <v>877</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="E17" s="12" t="s">
         <v>916</v>
       </c>
-      <c r="D16" s="12" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>918</v>
       </c>
-      <c r="D17" s="12" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12" t="s">
-        <v>879</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>920</v>
       </c>
-      <c r="D18" s="12" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="D19" s="12" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12" t="s">
-        <v>881</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="E22" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="D20" s="12" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>926</v>
       </c>
-      <c r="D21" s="12" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>928</v>
       </c>
-      <c r="D22" s="12" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12" t="s">
-        <v>884</v>
-      </c>
-      <c r="C23" s="12" t="s">
+      <c r="E25" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>932</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12" t="s">
-        <v>886</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>934</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>887</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>936</v>
-      </c>
       <c r="D26" s="12" t="s">
-        <v>937</v>
-      </c>
+        <v>1136</v>
+      </c>
+      <c r="E26" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6254,74 +7123,74 @@
         <v>706</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="I1" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>948</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>943</v>
+      </c>
+      <c r="L1" s="18" t="s">
         <v>949</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>955</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>950</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>956</v>
-      </c>
       <c r="M1" s="18" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
-        <v>938</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="A2" s="26" t="s">
+        <v>931</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="C3" s="14">
         <v>1</v>
@@ -6334,19 +7203,19 @@
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="12" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="12" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="L3" s="14"/>
       <c r="M3" s="12" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
@@ -6354,10 +7223,10 @@
     </row>
     <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="C4" s="14">
         <v>1</v>
@@ -6370,21 +7239,21 @@
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="12" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="L4" s="14"/>
       <c r="M4" s="12" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
@@ -6392,10 +7261,10 @@
     </row>
     <row r="5" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="C5" s="14">
         <v>1</v>
@@ -6408,15 +7277,15 @@
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="H5" s="14"/>
       <c r="I5" s="12" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="12" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="L5" s="14"/>
       <c r="M5" s="12"/>
@@ -6426,10 +7295,10 @@
     </row>
     <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="C6" s="14">
         <v>2</v>
@@ -6442,15 +7311,15 @@
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="12" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="L6" s="14"/>
       <c r="M6" s="12"/>
@@ -6460,10 +7329,10 @@
     </row>
     <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="C7" s="14">
         <v>2</v>
@@ -6476,15 +7345,15 @@
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="12" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="12" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="L7" s="14"/>
       <c r="M7" s="12"/>
@@ -6494,10 +7363,10 @@
     </row>
     <row r="8" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="C8" s="14">
         <v>2</v>
@@ -6510,15 +7379,15 @@
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="12" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="L8" s="14"/>
       <c r="M8" s="12"/>
@@ -6528,10 +7397,10 @@
     </row>
     <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="C9" s="14">
         <v>2</v>
@@ -6543,26 +7412,26 @@
         <v>3</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="12" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
@@ -6570,10 +7439,10 @@
     </row>
     <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="C10" s="14">
         <v>2</v>
@@ -6585,35 +7454,35 @@
         <v>2</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="12" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="L10" s="14"/>
       <c r="M10" s="12" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
     </row>
     <row r="11" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
-        <v>1021</v>
+      <c r="A11" s="25" t="s">
+        <v>1014</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="C11" s="14">
         <v>2</v>
@@ -6626,17 +7495,17 @@
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="L11" s="14"/>
       <c r="M11" s="12"/>
@@ -6646,10 +7515,10 @@
     </row>
     <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="C12" s="14">
         <v>2</v>
@@ -6662,17 +7531,17 @@
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="12"/>
@@ -6682,10 +7551,10 @@
     </row>
     <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="C13" s="14">
         <v>2</v>
@@ -6698,17 +7567,17 @@
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="12"/>
@@ -6718,29 +7587,29 @@
     </row>
     <row r="14" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="12" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="12" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="12" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
@@ -6748,10 +7617,10 @@
     </row>
     <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -6764,19 +7633,19 @@
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="12" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="12" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="L15" s="14"/>
       <c r="M15" s="12" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
@@ -6784,10 +7653,10 @@
     </row>
     <row r="16" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="C16" s="14">
         <v>2</v>
@@ -6800,19 +7669,19 @@
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="12" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="12" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="L16" s="14"/>
       <c r="M16" s="12" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="N16" s="12"/>
       <c r="O16" s="12"/>
@@ -6820,10 +7689,10 @@
     </row>
     <row r="17" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="C17" s="14">
         <v>2</v>
@@ -6836,54 +7705,54 @@
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="12" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="12" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="12" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="12" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="35" t="s">
-        <v>939</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
+      <c r="A18" s="26" t="s">
+        <v>932</v>
+      </c>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="C19" s="14">
         <v>3</v>
@@ -6895,20 +7764,20 @@
         <v>4</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="L19" s="14"/>
       <c r="M19" s="12"/>
@@ -6918,10 +7787,10 @@
     </row>
     <row r="20" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="C20" s="14">
         <v>3</v>
@@ -6933,20 +7802,20 @@
         <v>4</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="12" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="L20" s="14"/>
       <c r="M20" s="12"/>
@@ -6956,10 +7825,10 @@
     </row>
     <row r="21" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="C21" s="14">
         <v>3</v>
@@ -6971,24 +7840,24 @@
         <v>4</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="12" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="12" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
@@ -6996,10 +7865,10 @@
     </row>
     <row r="22" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="C22" s="14">
         <v>3</v>
@@ -7011,24 +7880,24 @@
         <v>4</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="12" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="12" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
@@ -7036,10 +7905,10 @@
     </row>
     <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C23" s="14">
         <v>3</v>
@@ -7052,17 +7921,17 @@
       </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="12"/>
@@ -7072,10 +7941,10 @@
     </row>
     <row r="24" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="C24" s="14">
         <v>3</v>
@@ -7088,17 +7957,17 @@
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="12"/>
@@ -7108,10 +7977,10 @@
     </row>
     <row r="25" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="C25" s="14">
         <v>3</v>
@@ -7126,19 +7995,19 @@
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="21" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K25" s="21" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="M25" s="21" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
@@ -7146,10 +8015,10 @@
     </row>
     <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="C26" s="14">
         <v>4</v>
@@ -7161,24 +8030,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="12" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="12" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
@@ -7186,10 +8055,10 @@
     </row>
     <row r="27" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="C27" s="14">
         <v>4</v>
@@ -7202,21 +8071,21 @@
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="12" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="12" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
@@ -7224,10 +8093,10 @@
     </row>
     <row r="28" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="C28" s="14">
         <v>3</v>
@@ -7240,21 +8109,21 @@
       </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="L28" s="14"/>
       <c r="M28" s="12" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
@@ -7262,10 +8131,10 @@
     </row>
     <row r="29" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="C29" s="14">
         <v>3</v>
@@ -7277,24 +8146,24 @@
         <v>3</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="L29" s="14"/>
       <c r="M29" s="12" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
@@ -7302,10 +8171,10 @@
     </row>
     <row r="30" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="C30" s="14">
         <v>3</v>
@@ -7317,37 +8186,37 @@
         <v>4</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="L30" s="14"/>
       <c r="M30" s="12" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="12" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="C31" s="14">
         <v>3</v>
@@ -7359,24 +8228,24 @@
         <v>4</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="12" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="L31" s="14"/>
       <c r="M31" s="12" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
@@ -7384,10 +8253,10 @@
     </row>
     <row r="32" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="C32" s="14">
         <v>3</v>
@@ -7399,26 +8268,26 @@
         <v>4</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="12" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
@@ -7426,10 +8295,10 @@
     </row>
     <row r="33" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="C33" s="14">
         <v>4</v>
@@ -7441,37 +8310,37 @@
         <v>3</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -7510,12 +8379,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -7654,12 +8523,12 @@
       <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
     </row>
     <row r="15" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -7798,12 +8667,12 @@
       <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
     </row>
     <row r="27" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
@@ -7942,12 +8811,12 @@
       <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
@@ -8086,12 +8955,12 @@
       <c r="D49" s="6"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="27"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="30"/>
     </row>
     <row r="51" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
@@ -8230,12 +9099,12 @@
       <c r="D61" s="6"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="25" t="s">
+      <c r="A62" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="27"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="30"/>
     </row>
     <row r="63" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
@@ -8374,12 +9243,12 @@
       <c r="D73" s="6"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="27"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="30"/>
     </row>
     <row r="75" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
@@ -8518,12 +9387,12 @@
       <c r="D85" s="6"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="25" t="s">
+      <c r="A86" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="27"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="30"/>
     </row>
     <row r="87" spans="1:4" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
@@ -8660,20 +9529,20 @@
       <c r="D97" s="6"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="28" t="s">
+      <c r="A98" s="31" t="s">
         <v>407</v>
       </c>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="30"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="33"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="25" t="s">
+      <c r="A99" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="27"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="30"/>
     </row>
     <row r="100" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
@@ -8810,12 +9679,12 @@
       <c r="D110" s="6"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="25" t="s">
+      <c r="A111" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="27"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
+      <c r="D111" s="30"/>
     </row>
     <row r="112" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
@@ -8952,12 +9821,12 @@
       <c r="D122" s="6"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="25" t="s">
+      <c r="A123" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
-      <c r="D123" s="27"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
+      <c r="D123" s="30"/>
     </row>
     <row r="124" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
@@ -9100,12 +9969,12 @@
       <c r="D135" s="6"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="27"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+      <c r="D136" s="30"/>
     </row>
     <row r="137" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
@@ -9252,12 +10121,12 @@
       <c r="D148" s="6"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="28" t="s">
         <v>335</v>
       </c>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="27"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
+      <c r="D149" s="30"/>
     </row>
     <row r="150" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
@@ -9394,12 +10263,12 @@
       <c r="D160" s="6"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="25" t="s">
+      <c r="A161" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="26"/>
-      <c r="C161" s="26"/>
-      <c r="D161" s="27"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="29"/>
+      <c r="D161" s="30"/>
     </row>
     <row r="162" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
@@ -9537,11 +10406,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A86:D86"/>
     <mergeCell ref="A98:D98"/>
@@ -9552,6 +10416,11 @@
     <mergeCell ref="A111:D111"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A50:D50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9581,11 +10450,11 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
     </row>
     <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -9654,11 +10523,11 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="35" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
     </row>
     <row r="10" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
@@ -9727,11 +10596,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="35" t="s">
         <v>595</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
     </row>
     <row r="17" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
@@ -9800,11 +10669,11 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="35" t="s">
         <v>596</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
     </row>
     <row r="24" spans="1:3" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
@@ -9894,10 +10763,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>659</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -9956,10 +10825,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="35" t="s">
         <v>658</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="35"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
